--- a/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_12_35.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_12_35.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2036747.632277949</v>
+        <v>2037818.755990225</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14697842.82031956</v>
+        <v>14697842.82031955</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14697842.82031956</v>
+        <v>14697842.82031955</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>657188.6984941055</v>
+        <v>657188.6984940858</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>657188.6984941055</v>
+        <v>657188.6984940858</v>
       </c>
     </row>
     <row r="11">
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>85.50414770182039</v>
+        <v>87.30283556964716</v>
       </c>
       <c r="T2" t="n">
         <v>184.8805867536895</v>
       </c>
       <c r="U2" t="n">
-        <v>250.9871803963368</v>
+        <v>249.1884925285102</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -736,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>257.4814473308688</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -748,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>209.5726123064429</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>133.6519859716245</v>
@@ -793,13 +793,13 @@
         <v>0.1959257979225981</v>
       </c>
       <c r="V3" t="n">
-        <v>14.51066719152016</v>
+        <v>374</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>190.3279297232695</v>
+        <v>374</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -909,10 +909,10 @@
         <v>3.34732203575993</v>
       </c>
       <c r="H5" t="n">
-        <v>5.608919435675552</v>
+        <v>3.81023156784903</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.79868786782652</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -973,16 +973,16 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>150.4346265429119</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1018,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>133.6519859716245</v>
+        <v>374</v>
       </c>
       <c r="S6" t="n">
         <v>62.48881128536601</v>
@@ -1030,10 +1030,10 @@
         <v>0.1959257979225981</v>
       </c>
       <c r="V6" t="n">
-        <v>14.51066719152016</v>
+        <v>374</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>265.2787621756744</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1149,7 +1149,7 @@
         <v>3.81023156784903</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.79868786782652</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>87.30283556964716</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T8" t="n">
         <v>184.8805867536895</v>
@@ -1216,7 +1216,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1264,19 +1264,19 @@
         <v>4.473444462796863</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1959257979225981</v>
+        <v>374</v>
       </c>
       <c r="V9" t="n">
-        <v>130.5815360723088</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>281.7394225040098</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1416,10 +1416,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>142.2280170485541</v>
+        <v>141.5319320520589</v>
       </c>
       <c r="T11" t="n">
-        <v>260.5210344205111</v>
+        <v>261.2171194170061</v>
       </c>
       <c r="U11" t="n">
         <v>330.1032663978569</v>
@@ -1459,13 +1459,13 @@
         <v>20.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>5.950139648612264</v>
+        <v>228.8924124088881</v>
       </c>
       <c r="H12" t="n">
         <v>5.544181526043758</v>
       </c>
       <c r="I12" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>212.2566464254573</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S12" t="n">
         <v>132.901311285366</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3.305168319657098</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M13" t="n">
         <v>97.89093927140237</v>
@@ -1562,7 +1562,7 @@
         <v>150.9111244520127</v>
       </c>
       <c r="O13" t="n">
-        <v>227.9026788331133</v>
+        <v>225.052317355647</v>
       </c>
       <c r="P13" t="n">
         <v>288.4057989676218</v>
@@ -1605,7 +1605,7 @@
         <v>162.9993129555745</v>
       </c>
       <c r="C14" t="n">
-        <v>129.778493246499</v>
+        <v>130.4745782429939</v>
       </c>
       <c r="D14" t="n">
         <v>91.33915573984979</v>
@@ -1617,10 +1617,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>83.28199540259408</v>
+        <v>83.28199540259411</v>
       </c>
       <c r="H14" t="n">
-        <v>73.89995518593946</v>
+        <v>73.89995518593948</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1656,7 +1656,7 @@
         <v>142.2280170485541</v>
       </c>
       <c r="T14" t="n">
-        <v>261.2171194170061</v>
+        <v>260.5210344205111</v>
       </c>
       <c r="U14" t="n">
         <v>330.1032663978569</v>
@@ -1684,10 +1684,10 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>42.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>28.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
         <v>23.67209722191262</v>
@@ -1696,13 +1696,13 @@
         <v>20.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>5.950139648612264</v>
+        <v>324.9501396486123</v>
       </c>
       <c r="H15" t="n">
-        <v>5.544181526043758</v>
+        <v>5.544181526043773</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1729,28 +1729,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>179.2619859716245</v>
+        <v>179.2619859716246</v>
       </c>
       <c r="S15" t="n">
-        <v>451.901311285366</v>
+        <v>165.8959717391988</v>
       </c>
       <c r="T15" t="n">
-        <v>306.1182172230725</v>
+        <v>83.17594446279683</v>
       </c>
       <c r="U15" t="n">
-        <v>81.15842579792258</v>
+        <v>81.1584257979226</v>
       </c>
       <c r="V15" t="n">
         <v>95.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>432.3731429098285</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X15" t="n">
         <v>100.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>399.3913927661343</v>
+        <v>80.39139276613435</v>
       </c>
     </row>
     <row r="16">
@@ -1790,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>6.155529797123449</v>
+        <v>6.155529797123435</v>
       </c>
       <c r="M16" t="n">
-        <v>97.89093927140237</v>
+        <v>97.89093927140236</v>
       </c>
       <c r="N16" t="n">
         <v>150.9111244520127</v>
@@ -1808,10 +1808,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>377.8450460139379</v>
+        <v>377.845046013938</v>
       </c>
       <c r="S16" t="n">
-        <v>28.98969199588275</v>
+        <v>28.98969199588089</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1918,16 +1918,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>288.4988294066022</v>
       </c>
       <c r="C18" t="n">
-        <v>361.0999124455193</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D18" t="n">
-        <v>251.879959657978</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>23.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
         <v>20.63624233787687</v>
@@ -1975,10 +1975,10 @@
         <v>83.17594446279685</v>
       </c>
       <c r="U18" t="n">
-        <v>81.15842579792258</v>
+        <v>400.1584257979226</v>
       </c>
       <c r="V18" t="n">
-        <v>95.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W18" t="n">
         <v>113.3731429098285</v>
@@ -1987,7 +1987,7 @@
         <v>100.8627394453875</v>
       </c>
       <c r="Y18" t="n">
-        <v>399.3913927661343</v>
+        <v>80.39139276613435</v>
       </c>
     </row>
     <row r="19">
@@ -2039,7 +2039,7 @@
         <v>227.9026788331133</v>
       </c>
       <c r="P19" t="n">
-        <v>285.5554374901554</v>
+        <v>288.4057989676218</v>
       </c>
       <c r="Q19" t="n">
         <v>351.422266425598</v>
@@ -2048,7 +2048,7 @@
         <v>377.8450460139379</v>
       </c>
       <c r="S19" t="n">
-        <v>31.84005347334727</v>
+        <v>28.98969199588095</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2091,10 +2091,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>83.28199540259411</v>
+        <v>82.58591040609919</v>
       </c>
       <c r="H20" t="n">
-        <v>73.20387018944457</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>288.4988294066021</v>
+        <v>65.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>361.0999124455193</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>251.8799596579784</v>
       </c>
       <c r="E21" t="n">
         <v>23.67209722191262</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G21" t="n">
-        <v>5.950139648612248</v>
+        <v>324.9501396486123</v>
       </c>
       <c r="H21" t="n">
-        <v>5.544181526043773</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2203,16 +2203,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>179.2619859716246</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S21" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T21" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U21" t="n">
-        <v>81.1584257979226</v>
+        <v>400.1584257979226</v>
       </c>
       <c r="V21" t="n">
         <v>95.51066719152016</v>
@@ -2221,7 +2221,7 @@
         <v>113.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y21" t="n">
         <v>80.39139276613435</v>
@@ -2264,10 +2264,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>6.155529797123435</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M22" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N22" t="n">
         <v>150.9111244520127</v>
@@ -2282,10 +2282,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S22" t="n">
-        <v>28.98969199588269</v>
+        <v>28.98969199588095</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2328,7 +2328,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>82.58591040609919</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H23" t="n">
         <v>73.89995518593946</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>142.2280170485541</v>
+        <v>141.5319320520589</v>
       </c>
       <c r="T23" t="n">
         <v>261.2171194170061</v>
@@ -2392,19 +2392,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>288.4988294066021</v>
+        <v>65.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>28.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G24" t="n">
         <v>5.950139648612264</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>179.2619859716245</v>
+        <v>498.2619859716245</v>
       </c>
       <c r="S24" t="n">
         <v>132.901311285366</v>
@@ -2452,7 +2452,7 @@
         <v>81.15842579792258</v>
       </c>
       <c r="V24" t="n">
-        <v>95.51066719152016</v>
+        <v>318.4529399517957</v>
       </c>
       <c r="W24" t="n">
         <v>113.3731429098285</v>
@@ -2522,7 +2522,7 @@
         <v>377.8450460139379</v>
       </c>
       <c r="S25" t="n">
-        <v>28.9896919958814</v>
+        <v>28.98969199588095</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2559,16 +2559,16 @@
         <v>91.33915573984979</v>
       </c>
       <c r="E26" t="n">
-        <v>85.36328960686865</v>
+        <v>84.66720461037373</v>
       </c>
       <c r="F26" t="n">
         <v>85.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>83.28199540259408</v>
+        <v>83.28199540259411</v>
       </c>
       <c r="H26" t="n">
-        <v>73.2038701894446</v>
+        <v>73.89995518593948</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2629,25 +2629,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>384.5565566463266</v>
+        <v>65.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>361.0999124455193</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>28.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>23.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
         <v>20.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>5.950139648612264</v>
+        <v>5.950139648612248</v>
       </c>
       <c r="H27" t="n">
-        <v>5.544181526043758</v>
+        <v>5.544181526043773</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,28 +2677,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>179.2619859716245</v>
+        <v>179.2619859716246</v>
       </c>
       <c r="S27" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T27" t="n">
-        <v>83.17594446279685</v>
+        <v>83.17594446279683</v>
       </c>
       <c r="U27" t="n">
-        <v>81.15842579792258</v>
+        <v>81.1584257979226</v>
       </c>
       <c r="V27" t="n">
         <v>95.51066719152016</v>
       </c>
       <c r="W27" t="n">
-        <v>113.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>323.805012205663</v>
+        <v>100.8627394453875</v>
       </c>
       <c r="Y27" t="n">
-        <v>399.3913927661343</v>
+        <v>303.3336655264099</v>
       </c>
     </row>
     <row r="28">
@@ -2738,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>3.305168319657098</v>
+        <v>6.155529797123435</v>
       </c>
       <c r="M28" t="n">
-        <v>97.89093927140237</v>
+        <v>97.89093927140236</v>
       </c>
       <c r="N28" t="n">
         <v>150.9111244520127</v>
@@ -2753,13 +2753,13 @@
         <v>288.4057989676218</v>
       </c>
       <c r="Q28" t="n">
-        <v>351.422266425598</v>
+        <v>348.5719049481316</v>
       </c>
       <c r="R28" t="n">
-        <v>377.8450460139379</v>
+        <v>377.845046013938</v>
       </c>
       <c r="S28" t="n">
-        <v>31.84005347334727</v>
+        <v>31.84005347334724</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2802,7 +2802,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>83.28199540259408</v>
+        <v>82.58591040609919</v>
       </c>
       <c r="H29" t="n">
         <v>73.89995518593946</v>
@@ -2838,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>141.5319320520589</v>
+        <v>142.2280170485541</v>
       </c>
       <c r="T29" t="n">
         <v>261.2171194170061</v>
@@ -2869,7 +2869,7 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>42.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D30" t="n">
         <v>28.93768689770263</v>
@@ -2878,7 +2878,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G30" t="n">
         <v>5.950139648612264</v>
@@ -2887,7 +2887,7 @@
         <v>5.544181526043758</v>
       </c>
       <c r="I30" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2914,19 +2914,19 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>212.2566464254569</v>
+        <v>498.2619859716245</v>
       </c>
       <c r="S30" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T30" t="n">
-        <v>402.1759444627968</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U30" t="n">
         <v>81.15842579792258</v>
       </c>
       <c r="V30" t="n">
-        <v>95.51066719152016</v>
+        <v>318.4529399517959</v>
       </c>
       <c r="W30" t="n">
         <v>113.3731429098285</v>
@@ -2990,10 +2990,10 @@
         <v>288.4057989676218</v>
       </c>
       <c r="Q31" t="n">
-        <v>351.422266425598</v>
+        <v>348.5719049481316</v>
       </c>
       <c r="R31" t="n">
-        <v>374.9946845364717</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S31" t="n">
         <v>31.84005347334727</v>
@@ -3039,10 +3039,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>83.28199540259411</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H32" t="n">
-        <v>73.89995518593948</v>
+        <v>73.2038701895459</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>261.2171194170061</v>
       </c>
       <c r="U32" t="n">
-        <v>329.4071814013618</v>
+        <v>330.1032663978569</v>
       </c>
       <c r="V32" t="n">
         <v>310.8510241668239</v>
@@ -3112,16 +3112,16 @@
         <v>28.93768689770263</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F33" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>5.950139648612248</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H33" t="n">
-        <v>5.544181526043773</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3151,25 +3151,25 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>179.2619859716246</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S33" t="n">
-        <v>451.901311285366</v>
+        <v>355.8435840456416</v>
       </c>
       <c r="T33" t="n">
-        <v>306.1182172230723</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U33" t="n">
-        <v>81.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V33" t="n">
-        <v>95.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W33" t="n">
         <v>113.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y33" t="n">
         <v>80.39139276613435</v>
@@ -3212,16 +3212,16 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>6.155529797123435</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M34" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N34" t="n">
         <v>150.9111244520127</v>
       </c>
       <c r="O34" t="n">
-        <v>225.0523173556467</v>
+        <v>227.9026788331133</v>
       </c>
       <c r="P34" t="n">
         <v>288.4057989676218</v>
@@ -3230,10 +3230,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S34" t="n">
-        <v>31.84005347334724</v>
+        <v>28.98969199588095</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3349,19 +3349,19 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>133.4029732681217</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>324.5441815260438</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>184.5126391076483</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3403,13 +3403,13 @@
         <v>17.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>35.37314290982852</v>
+        <v>374.0000000000364</v>
       </c>
       <c r="X36" t="n">
         <v>22.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>374</v>
+        <v>2.391392766134345</v>
       </c>
     </row>
     <row r="37">
@@ -3549,13 +3549,13 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>60.92708723799848</v>
+        <v>64.22801704855405</v>
       </c>
       <c r="T38" t="n">
         <v>183.2171194170061</v>
       </c>
       <c r="U38" t="n">
-        <v>252.1032663978569</v>
+        <v>248.8023365873013</v>
       </c>
       <c r="V38" t="n">
         <v>232.8510241668239</v>
@@ -3580,22 +3580,22 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>324.9501396486123</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>324.5441815260438</v>
       </c>
       <c r="I39" t="n">
         <v>189.9476123064429</v>
@@ -3631,13 +3631,13 @@
         <v>54.90131128536602</v>
       </c>
       <c r="T39" t="n">
-        <v>374</v>
+        <v>5.175944462796835</v>
       </c>
       <c r="U39" t="n">
-        <v>310.4982509017833</v>
+        <v>3.158425797922597</v>
       </c>
       <c r="V39" t="n">
-        <v>17.51066719152016</v>
+        <v>25.75241143432114</v>
       </c>
       <c r="W39" t="n">
         <v>35.37314290982852</v>
@@ -3738,13 +3738,13 @@
         <v>188.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>5.774687815990712</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>117.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>111.3632896068686</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>160.0149091563759</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -3795,13 +3795,13 @@
         <v>356.1032663978569</v>
       </c>
       <c r="V41" t="n">
-        <v>336.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>345.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>299.2818334606677</v>
       </c>
       <c r="Y41" t="n">
         <v>218.3174326828064</v>
@@ -3829,10 +3829,10 @@
         <v>46.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>31.95013964861226</v>
+        <v>31.95013964861225</v>
       </c>
       <c r="H42" t="n">
-        <v>33.93095497146885</v>
+        <v>31.54418152604377</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3862,13 +3862,13 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>205.2619859716245</v>
+        <v>205.2619859716246</v>
       </c>
       <c r="S42" t="n">
         <v>158.901311285366</v>
       </c>
       <c r="T42" t="n">
-        <v>109.1759444627968</v>
+        <v>111.562717908222</v>
       </c>
       <c r="U42" t="n">
         <v>107.1584257979226</v>
@@ -3929,13 +3929,13 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>176.9111244520127</v>
       </c>
       <c r="O43" t="n">
-        <v>1.555623315721627</v>
+        <v>139.0502978313306</v>
       </c>
       <c r="P43" t="n">
-        <v>314.4057989676218</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>374</v>
@@ -3944,7 +3944,7 @@
         <v>374</v>
       </c>
       <c r="S43" t="n">
-        <v>57.84005347334727</v>
+        <v>57.84005347334724</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3972,25 +3972,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>66.77522969307155</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>156.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>117.3391557398498</v>
+        <v>42.32542859328984</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>111.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>109.2819954025941</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>99.89995518593948</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4026,7 +4026,7 @@
         <v>168.2280170485541</v>
       </c>
       <c r="T44" t="n">
-        <v>287.2171194170061</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
         <v>356.1032663978569</v>
@@ -4035,13 +4035,13 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>345.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>299.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>218.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -4069,7 +4069,7 @@
         <v>31.95013964861225</v>
       </c>
       <c r="H45" t="n">
-        <v>33.93095497146896</v>
+        <v>31.54418152604377</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.386773445425144</v>
       </c>
       <c r="R45" t="n">
         <v>205.2619859716246</v>
@@ -4160,25 +4160,25 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>32.15552979712344</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>176.9111244520127</v>
       </c>
       <c r="O46" t="n">
-        <v>1.555623315721627</v>
+        <v>166.4889690663782</v>
       </c>
       <c r="P46" t="n">
         <v>314.4057989676218</v>
       </c>
       <c r="Q46" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>374</v>
+        <v>374.0000000002074</v>
       </c>
       <c r="S46" t="n">
         <v>57.84005347334724</v>
@@ -4321,25 +4321,25 @@
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K2" t="n">
-        <v>81.5583303517588</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L2" t="n">
-        <v>145.6202453266332</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="M2" t="n">
-        <v>515.8802453266331</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="N2" t="n">
-        <v>515.8802453266331</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="O2" t="n">
-        <v>886.1402453266331</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="P2" t="n">
-        <v>1256.400245326633</v>
+        <v>1125.74</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
@@ -4348,10 +4348,10 @@
         <v>1496</v>
       </c>
       <c r="S2" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.815317606417</v>
       </c>
       <c r="T2" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.067250178448</v>
       </c>
       <c r="U2" t="n">
         <v>969.3617021698518</v>
@@ -4376,22 +4376,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>907.0147105214633</v>
+        <v>504.9057470428903</v>
       </c>
       <c r="C3" t="n">
-        <v>907.0147105214633</v>
+        <v>244.8234770117097</v>
       </c>
       <c r="D3" t="n">
-        <v>907.0147105214633</v>
+        <v>244.8234770117097</v>
       </c>
       <c r="E3" t="n">
-        <v>907.0147105214633</v>
+        <v>244.8234770117097</v>
       </c>
       <c r="F3" t="n">
-        <v>907.0147105214633</v>
+        <v>244.8234770117097</v>
       </c>
       <c r="G3" t="n">
-        <v>578.2064886541781</v>
+        <v>244.8234770117097</v>
       </c>
       <c r="H3" t="n">
         <v>244.8234770117097</v>
@@ -4421,31 +4421,31 @@
         <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1349.46108157432</v>
+        <v>1496</v>
       </c>
       <c r="R3" t="n">
-        <v>1214.459075542376</v>
+        <v>1360.997993968056</v>
       </c>
       <c r="S3" t="n">
-        <v>1151.339064143017</v>
+        <v>1297.877982568697</v>
       </c>
       <c r="T3" t="n">
-        <v>1146.820433372515</v>
+        <v>1293.359351798195</v>
       </c>
       <c r="U3" t="n">
-        <v>1146.622528526128</v>
+        <v>1293.161446951808</v>
       </c>
       <c r="V3" t="n">
-        <v>1131.965288938734</v>
+        <v>915.3836691740303</v>
       </c>
       <c r="W3" t="n">
-        <v>1099.265144585372</v>
+        <v>882.6835248206681</v>
       </c>
       <c r="X3" t="n">
-        <v>907.0147105214633</v>
+        <v>504.9057470428903</v>
       </c>
       <c r="Y3" t="n">
-        <v>907.0147105214633</v>
+        <v>504.9057470428903</v>
       </c>
     </row>
     <row r="4">
@@ -4455,28 +4455,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>910.7837503381616</v>
+        <v>764.8620694109511</v>
       </c>
       <c r="C4" t="n">
-        <v>1036.785756156597</v>
+        <v>764.8620694109511</v>
       </c>
       <c r="D4" t="n">
-        <v>1150.104900281597</v>
+        <v>764.8620694109511</v>
       </c>
       <c r="E4" t="n">
-        <v>1150.104900281597</v>
+        <v>859.1344669130594</v>
       </c>
       <c r="F4" t="n">
-        <v>1150.104900281597</v>
+        <v>859.1344669130594</v>
       </c>
       <c r="G4" t="n">
-        <v>1303.69356125045</v>
+        <v>1012.723127881912</v>
       </c>
       <c r="H4" t="n">
-        <v>1303.69356125045</v>
+        <v>1012.723127881912</v>
       </c>
       <c r="I4" t="n">
-        <v>1382.983127881912</v>
+        <v>1012.723127881912</v>
       </c>
       <c r="J4" t="n">
         <v>1382.983127881912</v>
@@ -4506,25 +4506,25 @@
         <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="T4" t="n">
-        <v>70.34367574991084</v>
+        <v>218.7737217817557</v>
       </c>
       <c r="U4" t="n">
-        <v>316.9048008472139</v>
+        <v>218.7737217817557</v>
       </c>
       <c r="V4" t="n">
-        <v>515.7261937331598</v>
+        <v>218.7737217817557</v>
       </c>
       <c r="W4" t="n">
-        <v>687.6171119928372</v>
+        <v>390.6646400414331</v>
       </c>
       <c r="X4" t="n">
-        <v>687.6171119928372</v>
+        <v>541.6954310656266</v>
       </c>
       <c r="Y4" t="n">
-        <v>799.0264126718695</v>
+        <v>653.1047317446589</v>
       </c>
     </row>
     <row r="5">
@@ -4552,22 +4552,22 @@
         <v>35.58557518755106</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92</v>
+        <v>31.736856432148</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="K5" t="n">
         <v>400.18</v>
       </c>
-      <c r="K5" t="n">
-        <v>697.3881081337421</v>
-      </c>
       <c r="L5" t="n">
-        <v>1067.648108133742</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>1067.648108133742</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="N5" t="n">
         <v>1067.648108133742</v>
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1222.526720202428</v>
+        <v>381.3722089875785</v>
       </c>
       <c r="C6" t="n">
-        <v>1070.572551977265</v>
+        <v>381.3722089875785</v>
       </c>
       <c r="D6" t="n">
-        <v>719.1203429896864</v>
+        <v>29.92</v>
       </c>
       <c r="E6" t="n">
-        <v>372.9869114524009</v>
+        <v>29.92</v>
       </c>
       <c r="F6" t="n">
         <v>29.92</v>
@@ -4661,28 +4661,28 @@
         <v>1492.786030368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1357.784024336592</v>
+        <v>1115.008252590758</v>
       </c>
       <c r="S6" t="n">
-        <v>1294.664012937232</v>
+        <v>1051.888241191398</v>
       </c>
       <c r="T6" t="n">
-        <v>1290.14538216673</v>
+        <v>1047.369610420896</v>
       </c>
       <c r="U6" t="n">
-        <v>1289.947477320344</v>
+        <v>1047.17170557451</v>
       </c>
       <c r="V6" t="n">
-        <v>1275.29023773295</v>
+        <v>669.393927796732</v>
       </c>
       <c r="W6" t="n">
-        <v>1242.590093379587</v>
+        <v>401.4355821647376</v>
       </c>
       <c r="X6" t="n">
-        <v>1222.526720202428</v>
+        <v>381.3722089875785</v>
       </c>
       <c r="Y6" t="n">
-        <v>1222.526720202428</v>
+        <v>381.3722089875785</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253.0866383453244</v>
+        <v>492.3317069811812</v>
       </c>
       <c r="C7" t="n">
-        <v>379.0886441637601</v>
+        <v>618.3337127996169</v>
       </c>
       <c r="D7" t="n">
-        <v>492.4077882887602</v>
+        <v>618.3337127996169</v>
       </c>
       <c r="E7" t="n">
-        <v>610.2366925001733</v>
+        <v>736.16261701103</v>
       </c>
       <c r="F7" t="n">
-        <v>734.5976650921087</v>
+        <v>736.16261701103</v>
       </c>
       <c r="G7" t="n">
-        <v>888.1863260609612</v>
+        <v>736.16261701103</v>
       </c>
       <c r="H7" t="n">
-        <v>1059.321902040031</v>
+        <v>786.1141532081242</v>
       </c>
       <c r="I7" t="n">
-        <v>1285.930876713819</v>
+        <v>1012.723127881912</v>
       </c>
       <c r="J7" t="n">
-        <v>1386.743548464727</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="K7" t="n">
-        <v>1386.743548464727</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="L7" t="n">
         <v>1386.743548464727</v>
@@ -4743,25 +4743,25 @@
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>29.92</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T7" t="n">
-        <v>29.92</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="U7" t="n">
-        <v>29.92</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="V7" t="n">
-        <v>29.92</v>
+        <v>269.1650686358568</v>
       </c>
       <c r="W7" t="n">
-        <v>29.92</v>
+        <v>269.1650686358568</v>
       </c>
       <c r="X7" t="n">
-        <v>29.92</v>
+        <v>269.1650686358568</v>
       </c>
       <c r="Y7" t="n">
-        <v>141.3293006790323</v>
+        <v>380.5743693148891</v>
       </c>
     </row>
     <row r="8">
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106.914147375084</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C8" t="n">
-        <v>56.9398259175144</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D8" t="n">
-        <v>46.49623426110047</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E8" t="n">
-        <v>42.08887102183921</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F8" t="n">
-        <v>37.14985212485754</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G8" t="n">
-        <v>33.76871875540306</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H8" t="n">
-        <v>29.92</v>
+        <v>31.736856432148</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
@@ -4822,25 +4822,25 @@
         <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1407.815317606417</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T8" t="n">
-        <v>1221.067250178448</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U8" t="n">
-        <v>969.3617021698518</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V8" t="n">
-        <v>737.1889504861913</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W8" t="n">
-        <v>496.4076616165473</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X8" t="n">
-        <v>302.1835874138526</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y8" t="n">
-        <v>189.7417362190987</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>727.505640524864</v>
+        <v>593.0617163678237</v>
       </c>
       <c r="C9" t="n">
-        <v>727.505640524864</v>
+        <v>593.0617163678237</v>
       </c>
       <c r="D9" t="n">
-        <v>376.0534315372855</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="E9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="F9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="G9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="H9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="I9" t="n">
         <v>29.92</v>
@@ -4907,19 +4907,19 @@
         <v>1290.14538216673</v>
       </c>
       <c r="U9" t="n">
-        <v>1289.947477320344</v>
+        <v>912.3676043889525</v>
       </c>
       <c r="V9" t="n">
-        <v>1158.046935833163</v>
+        <v>897.7103648015584</v>
       </c>
       <c r="W9" t="n">
-        <v>1125.346791479801</v>
+        <v>613.1250895449829</v>
       </c>
       <c r="X9" t="n">
-        <v>1105.283418302642</v>
+        <v>593.0617163678237</v>
       </c>
       <c r="Y9" t="n">
-        <v>727.505640524864</v>
+        <v>593.0617163678237</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>329.8693446184157</v>
+        <v>518.4570086106736</v>
       </c>
       <c r="C10" t="n">
-        <v>329.8693446184157</v>
+        <v>518.4570086106736</v>
       </c>
       <c r="D10" t="n">
-        <v>329.8693446184157</v>
+        <v>518.4570086106736</v>
       </c>
       <c r="E10" t="n">
-        <v>329.8693446184157</v>
+        <v>636.2859128220866</v>
       </c>
       <c r="F10" t="n">
-        <v>329.8693446184157</v>
+        <v>636.2859128220866</v>
       </c>
       <c r="G10" t="n">
-        <v>483.4580055872682</v>
+        <v>789.8745737909392</v>
       </c>
       <c r="H10" t="n">
-        <v>654.5935815663379</v>
+        <v>789.8745737909392</v>
       </c>
       <c r="I10" t="n">
-        <v>881.2025562401257</v>
+        <v>1016.483548464727</v>
       </c>
       <c r="J10" t="n">
-        <v>1251.462556240126</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K10" t="n">
-        <v>1382.983127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L10" t="n">
         <v>1386.743548464727</v>
@@ -4983,22 +4983,22 @@
         <v>70.34367574991084</v>
       </c>
       <c r="T10" t="n">
-        <v>259.1973975316665</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="U10" t="n">
-        <v>329.8693446184157</v>
+        <v>316.9048008472139</v>
       </c>
       <c r="V10" t="n">
-        <v>329.8693446184157</v>
+        <v>316.9048008472139</v>
       </c>
       <c r="W10" t="n">
-        <v>329.8693446184157</v>
+        <v>488.7957191068913</v>
       </c>
       <c r="X10" t="n">
-        <v>329.8693446184157</v>
+        <v>488.7957191068913</v>
       </c>
       <c r="Y10" t="n">
-        <v>329.8693446184157</v>
+        <v>488.7957191068913</v>
       </c>
     </row>
     <row r="11">
@@ -5032,25 +5032,25 @@
         <v>52.4</v>
       </c>
       <c r="J11" t="n">
-        <v>567.6776741934345</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K11" t="n">
-        <v>1216.127674193434</v>
+        <v>790.1259849731395</v>
       </c>
       <c r="L11" t="n">
-        <v>1864.577674193434</v>
+        <v>1438.575984973139</v>
       </c>
       <c r="M11" t="n">
-        <v>2233.691587554807</v>
+        <v>1438.575984973139</v>
       </c>
       <c r="N11" t="n">
-        <v>2233.691587554807</v>
+        <v>2087.02598497314</v>
       </c>
       <c r="O11" t="n">
-        <v>2410.244759641279</v>
+        <v>2263.579157059612</v>
       </c>
       <c r="P11" t="n">
-        <v>2620</v>
+        <v>2473.334397418333</v>
       </c>
       <c r="Q11" t="n">
         <v>2620</v>
@@ -5059,7 +5059,7 @@
         <v>2620</v>
       </c>
       <c r="S11" t="n">
-        <v>2476.335336314592</v>
+        <v>2477.038452472668</v>
       </c>
       <c r="T11" t="n">
         <v>2213.182776293874</v>
@@ -5087,25 +5087,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>694.609972105162</v>
+        <v>727.9379119575185</v>
       </c>
       <c r="C12" t="n">
-        <v>329.8625857965566</v>
+        <v>363.1905256489131</v>
       </c>
       <c r="D12" t="n">
-        <v>300.6325990312004</v>
+        <v>333.9605388835569</v>
       </c>
       <c r="E12" t="n">
-        <v>276.7213897161371</v>
+        <v>310.0493295684936</v>
       </c>
       <c r="F12" t="n">
-        <v>255.8767004859585</v>
+        <v>289.204640338315</v>
       </c>
       <c r="G12" t="n">
-        <v>249.8664584166532</v>
+        <v>58.00018335964016</v>
       </c>
       <c r="H12" t="n">
-        <v>244.266275057013</v>
+        <v>52.4</v>
       </c>
       <c r="I12" t="n">
         <v>52.4</v>
@@ -5135,28 +5135,28 @@
         <v>2313.990605368536</v>
       </c>
       <c r="R12" t="n">
-        <v>2099.589952413528</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S12" t="n">
-        <v>1965.346203640431</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T12" t="n">
-        <v>1881.330098122455</v>
+        <v>1914.658037974811</v>
       </c>
       <c r="U12" t="n">
-        <v>1477.129668023543</v>
+        <v>1510.457607875899</v>
       </c>
       <c r="V12" t="n">
-        <v>1380.654246617967</v>
+        <v>1413.982186470324</v>
       </c>
       <c r="W12" t="n">
-        <v>943.9136982242009</v>
+        <v>977.2416380765574</v>
       </c>
       <c r="X12" t="n">
-        <v>842.0321432288599</v>
+        <v>875.3600830812164</v>
       </c>
       <c r="Y12" t="n">
-        <v>760.8287161923606</v>
+        <v>794.1566560447171</v>
       </c>
     </row>
     <row r="13">
@@ -5196,13 +5196,13 @@
         <v>1597.372803794637</v>
       </c>
       <c r="L13" t="n">
-        <v>1594.034249936398</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M13" t="n">
-        <v>1495.154513298618</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N13" t="n">
-        <v>1342.71903405416</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O13" t="n">
         <v>1112.514307960106</v>
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>607.5035534240029</v>
+        <v>608.2066695820786</v>
       </c>
       <c r="C14" t="n">
         <v>476.4141663063272</v>
@@ -5275,19 +5275,19 @@
         <v>790.1259849731395</v>
       </c>
       <c r="L14" t="n">
-        <v>1198.666868388498</v>
+        <v>1438.575984973139</v>
       </c>
       <c r="M14" t="n">
-        <v>1198.666868388498</v>
+        <v>2087.025984973141</v>
       </c>
       <c r="N14" t="n">
-        <v>1198.666868388498</v>
+        <v>2233.691587554807</v>
       </c>
       <c r="O14" t="n">
-        <v>1375.22004047497</v>
+        <v>2410.244759641279</v>
       </c>
       <c r="P14" t="n">
-        <v>2023.670040474971</v>
+        <v>2620</v>
       </c>
       <c r="Q14" t="n">
         <v>2620</v>
@@ -5299,22 +5299,22 @@
         <v>2476.335336314592</v>
       </c>
       <c r="T14" t="n">
-        <v>2212.479660135798</v>
+        <v>2213.182776293874</v>
       </c>
       <c r="U14" t="n">
-        <v>1879.04201730968</v>
+        <v>1879.745133467756</v>
       </c>
       <c r="V14" t="n">
-        <v>1565.051083807838</v>
+        <v>1565.754199965913</v>
       </c>
       <c r="W14" t="n">
-        <v>1242.451613120012</v>
+        <v>1243.154729278087</v>
       </c>
       <c r="X14" t="n">
-        <v>966.4093570991351</v>
+        <v>967.1124732572108</v>
       </c>
       <c r="Y14" t="n">
-        <v>772.1493240861994</v>
+        <v>772.852440244275</v>
       </c>
     </row>
     <row r="15">
@@ -5324,25 +5324,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>180.5214748259267</v>
+        <v>1339.054416549606</v>
       </c>
       <c r="C15" t="n">
-        <v>137.9963107395436</v>
+        <v>974.307030241001</v>
       </c>
       <c r="D15" t="n">
-        <v>108.7663239741874</v>
+        <v>622.8548212534226</v>
       </c>
       <c r="E15" t="n">
-        <v>84.85511465912413</v>
+        <v>598.9436119383594</v>
       </c>
       <c r="F15" t="n">
-        <v>64.01042542894548</v>
+        <v>578.0989227081807</v>
       </c>
       <c r="G15" t="n">
-        <v>58.00018335964016</v>
+        <v>249.8664584166532</v>
       </c>
       <c r="H15" t="n">
-        <v>52.4</v>
+        <v>244.266275057013</v>
       </c>
       <c r="I15" t="n">
         <v>52.4</v>
@@ -5375,25 +5375,25 @@
         <v>2132.917892265885</v>
       </c>
       <c r="S15" t="n">
-        <v>1676.451921270565</v>
+        <v>1965.346203640431</v>
       </c>
       <c r="T15" t="n">
-        <v>1367.241600843219</v>
+        <v>1881.330098122455</v>
       </c>
       <c r="U15" t="n">
-        <v>1285.26339296653</v>
+        <v>1799.351890245765</v>
       </c>
       <c r="V15" t="n">
-        <v>1188.787971560954</v>
+        <v>1702.876468840189</v>
       </c>
       <c r="W15" t="n">
-        <v>752.0474231671878</v>
+        <v>1588.358142668645</v>
       </c>
       <c r="X15" t="n">
-        <v>650.1658681718469</v>
+        <v>1486.476587673304</v>
       </c>
       <c r="Y15" t="n">
-        <v>246.7402189131253</v>
+        <v>1405.273160636805</v>
       </c>
     </row>
     <row r="16">
@@ -5403,55 +5403,55 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>673.4417775581345</v>
+        <v>673.4417775581344</v>
       </c>
       <c r="C16" t="n">
-        <v>719.2537833765723</v>
+        <v>719.2537833765701</v>
       </c>
       <c r="D16" t="n">
-        <v>752.3829275015723</v>
+        <v>752.3829275015702</v>
       </c>
       <c r="E16" t="n">
-        <v>790.0218317129853</v>
+        <v>790.0218317129832</v>
       </c>
       <c r="F16" t="n">
-        <v>834.1928043049209</v>
+        <v>834.1928043049187</v>
       </c>
       <c r="G16" t="n">
-        <v>908.0645554377078</v>
+        <v>908.0645554377056</v>
       </c>
       <c r="H16" t="n">
-        <v>1003.216333056122</v>
+        <v>1003.21633305612</v>
       </c>
       <c r="I16" t="n">
-        <v>1163.862419205319</v>
+        <v>1163.862419205317</v>
       </c>
       <c r="J16" t="n">
-        <v>1491.077756743017</v>
+        <v>1491.077756743014</v>
       </c>
       <c r="K16" t="n">
-        <v>1597.372803794639</v>
+        <v>1597.372803794637</v>
       </c>
       <c r="L16" t="n">
-        <v>1591.155096928858</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M16" t="n">
-        <v>1492.275360291078</v>
+        <v>1492.275360291075</v>
       </c>
       <c r="N16" t="n">
-        <v>1339.83988104662</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O16" t="n">
-        <v>1109.635154952566</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P16" t="n">
-        <v>818.3161660963825</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.3441798078997</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R16" t="n">
-        <v>81.68251716755833</v>
+        <v>81.68251716755645</v>
       </c>
       <c r="S16" t="n">
         <v>52.4</v>
@@ -5460,19 +5460,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U16" t="n">
-        <v>329.4820370429932</v>
+        <v>329.4820370429931</v>
       </c>
       <c r="V16" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W16" t="n">
-        <v>539.8143481886166</v>
+        <v>539.8143481886165</v>
       </c>
       <c r="X16" t="n">
-        <v>610.6551392128101</v>
+        <v>610.65513921281</v>
       </c>
       <c r="Y16" t="n">
-        <v>641.8744398918424</v>
+        <v>641.8744398918423</v>
       </c>
     </row>
     <row r="17">
@@ -5512,13 +5512,13 @@
         <v>327.4727226113304</v>
       </c>
       <c r="L17" t="n">
-        <v>936.791587554806</v>
+        <v>557.9700049228883</v>
       </c>
       <c r="M17" t="n">
-        <v>1585.241587554807</v>
+        <v>1206.42000492289</v>
       </c>
       <c r="N17" t="n">
-        <v>2233.691587554807</v>
+        <v>1854.870004922892</v>
       </c>
       <c r="O17" t="n">
         <v>2410.244759641279</v>
@@ -5561,13 +5561,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>727.9379119575181</v>
+        <v>502.743697048149</v>
       </c>
       <c r="C18" t="n">
-        <v>363.1905256489127</v>
+        <v>460.2185329617658</v>
       </c>
       <c r="D18" t="n">
-        <v>108.7663239741874</v>
+        <v>430.9885461964096</v>
       </c>
       <c r="E18" t="n">
         <v>84.85511465912413</v>
@@ -5618,19 +5618,19 @@
         <v>1914.658037974811</v>
       </c>
       <c r="U18" t="n">
-        <v>1832.679830098122</v>
+        <v>1510.457607875899</v>
       </c>
       <c r="V18" t="n">
-        <v>1736.204408692546</v>
+        <v>1091.759964248101</v>
       </c>
       <c r="W18" t="n">
-        <v>1621.686082521002</v>
+        <v>977.2416380765571</v>
       </c>
       <c r="X18" t="n">
-        <v>1519.804527525661</v>
+        <v>875.3600830812162</v>
       </c>
       <c r="Y18" t="n">
-        <v>1116.378878266939</v>
+        <v>794.1566560447169</v>
       </c>
     </row>
     <row r="19">
@@ -5682,13 +5682,13 @@
         <v>1109.635154952564</v>
       </c>
       <c r="P19" t="n">
-        <v>821.1953191039224</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q19" t="n">
-        <v>466.2233328154396</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R19" t="n">
-        <v>84.56167017509824</v>
+        <v>81.68251716755651</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -5734,7 +5734,7 @@
         <v>210.4665309010492</v>
       </c>
       <c r="G20" t="n">
-        <v>126.3433032216612</v>
+        <v>127.0464193797368</v>
       </c>
       <c r="H20" t="n">
         <v>52.4</v>
@@ -5746,13 +5746,13 @@
         <v>141.6759849731395</v>
       </c>
       <c r="K20" t="n">
-        <v>706.2943052432483</v>
+        <v>327.4727226113304</v>
       </c>
       <c r="L20" t="n">
-        <v>936.791587554806</v>
+        <v>936.7915875547992</v>
       </c>
       <c r="M20" t="n">
-        <v>1585.241587554807</v>
+        <v>1585.241587554803</v>
       </c>
       <c r="N20" t="n">
         <v>2233.691587554807</v>
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1147.188141492594</v>
+        <v>727.9379119575184</v>
       </c>
       <c r="C21" t="n">
-        <v>782.4407551839881</v>
+        <v>685.4127478711353</v>
       </c>
       <c r="D21" t="n">
-        <v>430.9885461964097</v>
+        <v>430.9885461964096</v>
       </c>
       <c r="E21" t="n">
         <v>407.0773368813464</v>
       </c>
       <c r="F21" t="n">
-        <v>64.01042542894548</v>
+        <v>386.2326476511677</v>
       </c>
       <c r="G21" t="n">
-        <v>58.00018335964018</v>
+        <v>58.00018335964016</v>
       </c>
       <c r="H21" t="n">
         <v>52.4</v>
@@ -5855,19 +5855,19 @@
         <v>1914.658037974811</v>
       </c>
       <c r="U21" t="n">
-        <v>1832.679830098122</v>
+        <v>1510.457607875899</v>
       </c>
       <c r="V21" t="n">
-        <v>1736.204408692546</v>
+        <v>1413.982186470324</v>
       </c>
       <c r="W21" t="n">
-        <v>1621.686082521002</v>
+        <v>1299.46386029878</v>
       </c>
       <c r="X21" t="n">
-        <v>1519.804527525661</v>
+        <v>875.3600830812163</v>
       </c>
       <c r="Y21" t="n">
-        <v>1438.601100489161</v>
+        <v>794.156656044717</v>
       </c>
     </row>
     <row r="22">
@@ -5877,55 +5877,55 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>673.4417775581344</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C22" t="n">
-        <v>719.2537833765701</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D22" t="n">
-        <v>752.3829275015702</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E22" t="n">
-        <v>790.0218317129832</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F22" t="n">
-        <v>834.1928043049187</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G22" t="n">
-        <v>908.0645554377056</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H22" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I22" t="n">
-        <v>1163.862419205319</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J22" t="n">
-        <v>1491.077756743016</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K22" t="n">
-        <v>1597.372803794639</v>
+        <v>1597.372803794637</v>
       </c>
       <c r="L22" t="n">
-        <v>1591.155096928857</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M22" t="n">
-        <v>1492.275360291077</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N22" t="n">
-        <v>1339.83988104662</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O22" t="n">
-        <v>1109.635154952566</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P22" t="n">
-        <v>818.3161660963825</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.3441798078997</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R22" t="n">
-        <v>81.68251716755827</v>
+        <v>81.68251716755651</v>
       </c>
       <c r="S22" t="n">
         <v>52.4</v>
@@ -5934,19 +5934,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U22" t="n">
-        <v>329.4820370429931</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V22" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W22" t="n">
-        <v>539.8143481886165</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X22" t="n">
-        <v>610.65513921281</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y22" t="n">
-        <v>641.8744398918423</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="23">
@@ -5956,19 +5956,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>607.5035534240029</v>
+        <v>608.2066695820786</v>
       </c>
       <c r="C23" t="n">
-        <v>475.7110501482515</v>
+        <v>476.4141663063272</v>
       </c>
       <c r="D23" t="n">
-        <v>383.4492766736557</v>
+        <v>384.1523928317314</v>
       </c>
       <c r="E23" t="n">
-        <v>297.2237316162127</v>
+        <v>297.9268477742883</v>
       </c>
       <c r="F23" t="n">
-        <v>210.4665309010492</v>
+        <v>211.1696470591248</v>
       </c>
       <c r="G23" t="n">
         <v>127.0464193797368</v>
@@ -5989,16 +5989,16 @@
         <v>1438.575984973139</v>
       </c>
       <c r="M23" t="n">
-        <v>1585.241587554807</v>
+        <v>1438.575984973139</v>
       </c>
       <c r="N23" t="n">
-        <v>2233.691587554807</v>
+        <v>1438.575984973139</v>
       </c>
       <c r="O23" t="n">
-        <v>2410.244759641279</v>
+        <v>2087.025984973143</v>
       </c>
       <c r="P23" t="n">
-        <v>2620</v>
+        <v>2296.781225331864</v>
       </c>
       <c r="Q23" t="n">
         <v>2620</v>
@@ -6007,25 +6007,25 @@
         <v>2620</v>
       </c>
       <c r="S23" t="n">
-        <v>2476.335336314592</v>
+        <v>2477.038452472668</v>
       </c>
       <c r="T23" t="n">
-        <v>2212.479660135798</v>
+        <v>2213.182776293874</v>
       </c>
       <c r="U23" t="n">
-        <v>1879.04201730968</v>
+        <v>1879.745133467756</v>
       </c>
       <c r="V23" t="n">
-        <v>1565.051083807838</v>
+        <v>1565.754199965913</v>
       </c>
       <c r="W23" t="n">
-        <v>1242.451613120012</v>
+        <v>1243.154729278087</v>
       </c>
       <c r="X23" t="n">
-        <v>966.4093570991351</v>
+        <v>967.1124732572108</v>
       </c>
       <c r="Y23" t="n">
-        <v>772.1493240861994</v>
+        <v>772.852440244275</v>
       </c>
     </row>
     <row r="24">
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1147.188141492594</v>
+        <v>824.9659192703713</v>
       </c>
       <c r="C24" t="n">
         <v>782.4407551839881</v>
       </c>
       <c r="D24" t="n">
-        <v>753.2107684186319</v>
+        <v>430.9885461964096</v>
       </c>
       <c r="E24" t="n">
-        <v>407.0773368813464</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F24" t="n">
         <v>64.01042542894548</v>
@@ -6083,28 +6083,28 @@
         <v>2313.990605368536</v>
       </c>
       <c r="R24" t="n">
-        <v>2132.917892265885</v>
+        <v>1810.695670043663</v>
       </c>
       <c r="S24" t="n">
-        <v>1998.674143492788</v>
+        <v>1676.451921270566</v>
       </c>
       <c r="T24" t="n">
-        <v>1914.658037974811</v>
+        <v>1592.435815752589</v>
       </c>
       <c r="U24" t="n">
-        <v>1832.679830098122</v>
+        <v>1510.457607875899</v>
       </c>
       <c r="V24" t="n">
-        <v>1736.204408692546</v>
+        <v>1188.787971560954</v>
       </c>
       <c r="W24" t="n">
-        <v>1621.686082521002</v>
+        <v>1074.26964538941</v>
       </c>
       <c r="X24" t="n">
-        <v>1519.804527525661</v>
+        <v>972.3880903940692</v>
       </c>
       <c r="Y24" t="n">
-        <v>1438.601100489161</v>
+        <v>891.1846633575699</v>
       </c>
     </row>
     <row r="25">
@@ -6129,7 +6129,7 @@
         <v>834.1928043049188</v>
       </c>
       <c r="G25" t="n">
-        <v>908.0645554377063</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H25" t="n">
         <v>1003.21633305612</v>
@@ -6141,7 +6141,7 @@
         <v>1491.077756743015</v>
       </c>
       <c r="K25" t="n">
-        <v>1597.372803794638</v>
+        <v>1597.372803794637</v>
       </c>
       <c r="L25" t="n">
         <v>1591.155096928856</v>
@@ -6150,19 +6150,19 @@
         <v>1492.275360291076</v>
       </c>
       <c r="N25" t="n">
-        <v>1339.839881046619</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O25" t="n">
-        <v>1109.635154952565</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P25" t="n">
-        <v>818.3161660963812</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.3441798078983</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R25" t="n">
-        <v>81.68251716755697</v>
+        <v>81.68251716755651</v>
       </c>
       <c r="S25" t="n">
         <v>52.4</v>
@@ -6202,13 +6202,13 @@
         <v>383.4492766736557</v>
       </c>
       <c r="E26" t="n">
-        <v>297.2237316162127</v>
+        <v>297.9268477742883</v>
       </c>
       <c r="F26" t="n">
-        <v>210.4665309010492</v>
+        <v>211.1696470591248</v>
       </c>
       <c r="G26" t="n">
-        <v>126.3433032216612</v>
+        <v>127.0464193797368</v>
       </c>
       <c r="H26" t="n">
         <v>52.4</v>
@@ -6220,22 +6220,22 @@
         <v>141.6759849731395</v>
       </c>
       <c r="K26" t="n">
-        <v>790.1259849731395</v>
+        <v>327.4727226113304</v>
       </c>
       <c r="L26" t="n">
-        <v>1438.575984973139</v>
+        <v>557.9700049228883</v>
       </c>
       <c r="M26" t="n">
-        <v>2087.02598497314</v>
+        <v>1206.420004922896</v>
       </c>
       <c r="N26" t="n">
-        <v>2233.691587554807</v>
+        <v>1206.420004922896</v>
       </c>
       <c r="O26" t="n">
-        <v>2410.244759641279</v>
+        <v>1854.870004922903</v>
       </c>
       <c r="P26" t="n">
-        <v>2620</v>
+        <v>2064.625245281623</v>
       </c>
       <c r="Q26" t="n">
         <v>2620</v>
@@ -6272,13 +6272,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>502.743697048149</v>
+        <v>824.9659192703713</v>
       </c>
       <c r="C27" t="n">
-        <v>137.9963107395436</v>
+        <v>782.4407551839881</v>
       </c>
       <c r="D27" t="n">
-        <v>108.7663239741874</v>
+        <v>430.9885461964096</v>
       </c>
       <c r="E27" t="n">
         <v>84.85511465912413</v>
@@ -6287,7 +6287,7 @@
         <v>64.01042542894548</v>
       </c>
       <c r="G27" t="n">
-        <v>58.00018335964016</v>
+        <v>58.00018335964018</v>
       </c>
       <c r="H27" t="n">
         <v>52.4</v>
@@ -6335,10 +6335,10 @@
         <v>1736.204408692546</v>
       </c>
       <c r="W27" t="n">
-        <v>1621.686082521002</v>
+        <v>1299.46386029878</v>
       </c>
       <c r="X27" t="n">
-        <v>1294.610312616292</v>
+        <v>1197.582305303438</v>
       </c>
       <c r="Y27" t="n">
         <v>891.1846633575699</v>
@@ -6351,55 +6351,55 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>673.4417775581345</v>
+        <v>673.4417775581344</v>
       </c>
       <c r="C28" t="n">
-        <v>719.2537833765703</v>
+        <v>719.2537833765701</v>
       </c>
       <c r="D28" t="n">
-        <v>752.3829275015703</v>
+        <v>752.3829275015702</v>
       </c>
       <c r="E28" t="n">
-        <v>790.0218317129833</v>
+        <v>790.0218317129832</v>
       </c>
       <c r="F28" t="n">
-        <v>834.1928043049188</v>
+        <v>834.1928043049187</v>
       </c>
       <c r="G28" t="n">
-        <v>908.0645554377057</v>
+        <v>908.0645554377056</v>
       </c>
       <c r="H28" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I28" t="n">
-        <v>1163.862419205318</v>
+        <v>1163.862419205317</v>
       </c>
       <c r="J28" t="n">
-        <v>1491.077756743015</v>
+        <v>1491.077756743014</v>
       </c>
       <c r="K28" t="n">
         <v>1597.372803794637</v>
       </c>
       <c r="L28" t="n">
-        <v>1594.034249936398</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M28" t="n">
-        <v>1495.154513298618</v>
+        <v>1492.275360291075</v>
       </c>
       <c r="N28" t="n">
-        <v>1342.71903405416</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O28" t="n">
-        <v>1112.514307960106</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P28" t="n">
-        <v>821.1953191039224</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q28" t="n">
-        <v>466.2233328154396</v>
+        <v>466.2233328154397</v>
       </c>
       <c r="R28" t="n">
-        <v>84.56167017509824</v>
+        <v>84.56167017509823</v>
       </c>
       <c r="S28" t="n">
         <v>52.4</v>
@@ -6408,19 +6408,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U28" t="n">
-        <v>329.4820370429932</v>
+        <v>329.4820370429931</v>
       </c>
       <c r="V28" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W28" t="n">
-        <v>539.8143481886166</v>
+        <v>539.8143481886165</v>
       </c>
       <c r="X28" t="n">
-        <v>610.6551392128101</v>
+        <v>610.65513921281</v>
       </c>
       <c r="Y28" t="n">
-        <v>641.8744398918424</v>
+        <v>641.8744398918423</v>
       </c>
     </row>
     <row r="29">
@@ -6430,19 +6430,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>608.2066695820786</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C29" t="n">
-        <v>476.4141663063272</v>
+        <v>475.7110501482515</v>
       </c>
       <c r="D29" t="n">
-        <v>384.1523928317314</v>
+        <v>383.4492766736557</v>
       </c>
       <c r="E29" t="n">
-        <v>297.9268477742883</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F29" t="n">
-        <v>211.1696470591248</v>
+        <v>210.4665309010492</v>
       </c>
       <c r="G29" t="n">
         <v>127.0464193797368</v>
@@ -6454,22 +6454,22 @@
         <v>52.4</v>
       </c>
       <c r="J29" t="n">
-        <v>567.6776741934345</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K29" t="n">
-        <v>753.4744118316256</v>
+        <v>790.1259849731395</v>
       </c>
       <c r="L29" t="n">
-        <v>983.9716941431833</v>
+        <v>1438.575984973139</v>
       </c>
       <c r="M29" t="n">
-        <v>1632.421694143186</v>
+        <v>1438.575984973139</v>
       </c>
       <c r="N29" t="n">
-        <v>1632.421694143186</v>
+        <v>1794.996827913518</v>
       </c>
       <c r="O29" t="n">
-        <v>1971.549999999997</v>
+        <v>1971.549999999991</v>
       </c>
       <c r="P29" t="n">
         <v>2620</v>
@@ -6481,25 +6481,25 @@
         <v>2620</v>
       </c>
       <c r="S29" t="n">
-        <v>2477.038452472668</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T29" t="n">
-        <v>2213.182776293874</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U29" t="n">
-        <v>1879.745133467756</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V29" t="n">
-        <v>1565.754199965913</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W29" t="n">
-        <v>1243.154729278087</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X29" t="n">
-        <v>967.1124732572108</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y29" t="n">
-        <v>772.852440244275</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="30">
@@ -6509,25 +6509,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1016.832194327384</v>
+        <v>824.9659192703712</v>
       </c>
       <c r="C30" t="n">
-        <v>974.3070302410013</v>
+        <v>460.2185329617658</v>
       </c>
       <c r="D30" t="n">
-        <v>945.077043475645</v>
+        <v>430.9885461964096</v>
       </c>
       <c r="E30" t="n">
-        <v>598.9436119383595</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F30" t="n">
-        <v>255.8767004859585</v>
+        <v>64.01042542894548</v>
       </c>
       <c r="G30" t="n">
-        <v>249.8664584166532</v>
+        <v>58.00018335964016</v>
       </c>
       <c r="H30" t="n">
-        <v>244.266275057013</v>
+        <v>52.4</v>
       </c>
       <c r="I30" t="n">
         <v>52.4</v>
@@ -6557,28 +6557,28 @@
         <v>2313.990605368536</v>
       </c>
       <c r="R30" t="n">
-        <v>2099.589952413529</v>
+        <v>1810.695670043663</v>
       </c>
       <c r="S30" t="n">
-        <v>1965.346203640432</v>
+        <v>1676.451921270566</v>
       </c>
       <c r="T30" t="n">
-        <v>1559.107875900233</v>
+        <v>1592.435815752589</v>
       </c>
       <c r="U30" t="n">
-        <v>1477.129668023543</v>
+        <v>1510.457607875899</v>
       </c>
       <c r="V30" t="n">
-        <v>1380.654246617967</v>
+        <v>1188.787971560954</v>
       </c>
       <c r="W30" t="n">
-        <v>1266.135920446423</v>
+        <v>1074.26964538941</v>
       </c>
       <c r="X30" t="n">
-        <v>1164.254365451082</v>
+        <v>972.3880903940691</v>
       </c>
       <c r="Y30" t="n">
-        <v>1083.050938414583</v>
+        <v>891.1846633575698</v>
       </c>
     </row>
     <row r="31">
@@ -6633,7 +6633,7 @@
         <v>818.3161660963807</v>
       </c>
       <c r="Q31" t="n">
-        <v>463.3441798078979</v>
+        <v>466.2233328154396</v>
       </c>
       <c r="R31" t="n">
         <v>84.56167017509824</v>
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>608.2066695820786</v>
+        <v>607.5035534241052</v>
       </c>
       <c r="C32" t="n">
-        <v>476.4141663063272</v>
+        <v>475.7110501483538</v>
       </c>
       <c r="D32" t="n">
-        <v>384.1523928317314</v>
+        <v>383.449276673758</v>
       </c>
       <c r="E32" t="n">
-        <v>297.9268477742883</v>
+        <v>297.223731616315</v>
       </c>
       <c r="F32" t="n">
-        <v>211.1696470591248</v>
+        <v>210.4665309011515</v>
       </c>
       <c r="G32" t="n">
-        <v>127.0464193797368</v>
+        <v>126.3433032217635</v>
       </c>
       <c r="H32" t="n">
         <v>52.4</v>
@@ -6700,10 +6700,10 @@
         <v>1438.575984973139</v>
       </c>
       <c r="M32" t="n">
-        <v>1585.241587554803</v>
+        <v>1438.575984973139</v>
       </c>
       <c r="N32" t="n">
-        <v>2233.691587554807</v>
+        <v>2087.025984973157</v>
       </c>
       <c r="O32" t="n">
         <v>2410.244759641279</v>
@@ -6715,28 +6715,28 @@
         <v>2620</v>
       </c>
       <c r="R32" t="n">
-        <v>2620</v>
+        <v>2620.000000000102</v>
       </c>
       <c r="S32" t="n">
-        <v>2476.335336314592</v>
+        <v>2476.335336314694</v>
       </c>
       <c r="T32" t="n">
-        <v>2212.479660135798</v>
+        <v>2212.4796601359</v>
       </c>
       <c r="U32" t="n">
-        <v>1879.745133467756</v>
+        <v>1879.042017309782</v>
       </c>
       <c r="V32" t="n">
-        <v>1565.754199965913</v>
+        <v>1565.05108380794</v>
       </c>
       <c r="W32" t="n">
-        <v>1243.154729278087</v>
+        <v>1242.451613120114</v>
       </c>
       <c r="X32" t="n">
-        <v>967.1124732572108</v>
+        <v>966.4093570992375</v>
       </c>
       <c r="Y32" t="n">
-        <v>772.852440244275</v>
+        <v>772.1493240863017</v>
       </c>
     </row>
     <row r="33">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>824.9659192703713</v>
+        <v>502.743697048149</v>
       </c>
       <c r="C33" t="n">
-        <v>782.4407551839881</v>
+        <v>460.2185329617659</v>
       </c>
       <c r="D33" t="n">
-        <v>753.2107684186319</v>
+        <v>430.9885461964097</v>
       </c>
       <c r="E33" t="n">
         <v>407.0773368813464</v>
@@ -6761,7 +6761,7 @@
         <v>64.01042542894548</v>
       </c>
       <c r="G33" t="n">
-        <v>58.00018335964018</v>
+        <v>58.00018335964016</v>
       </c>
       <c r="H33" t="n">
         <v>52.4</v>
@@ -6797,13 +6797,13 @@
         <v>2132.917892265885</v>
       </c>
       <c r="S33" t="n">
-        <v>1676.451921270565</v>
+        <v>1773.479928583419</v>
       </c>
       <c r="T33" t="n">
-        <v>1367.24160084322</v>
+        <v>1689.463823065442</v>
       </c>
       <c r="U33" t="n">
-        <v>1285.26339296653</v>
+        <v>1607.485615188752</v>
       </c>
       <c r="V33" t="n">
         <v>1188.787971560954</v>
@@ -6812,10 +6812,10 @@
         <v>1074.26964538941</v>
       </c>
       <c r="X33" t="n">
-        <v>972.3880903940692</v>
+        <v>650.1658681718469</v>
       </c>
       <c r="Y33" t="n">
-        <v>891.1846633575699</v>
+        <v>568.9624411353476</v>
       </c>
     </row>
     <row r="34">
@@ -6825,31 +6825,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>673.4417775581344</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C34" t="n">
-        <v>719.2537833765701</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D34" t="n">
-        <v>752.3829275015702</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E34" t="n">
-        <v>790.0218317129832</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F34" t="n">
-        <v>834.1928043049187</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G34" t="n">
-        <v>908.0645554377056</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H34" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I34" t="n">
-        <v>1163.862419205317</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J34" t="n">
-        <v>1491.077756743014</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K34" t="n">
         <v>1597.372803794637</v>
@@ -6858,22 +6858,22 @@
         <v>1591.155096928856</v>
       </c>
       <c r="M34" t="n">
-        <v>1492.275360291075</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N34" t="n">
         <v>1339.839881046618</v>
       </c>
       <c r="O34" t="n">
-        <v>1112.514307960106</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P34" t="n">
-        <v>821.1953191039224</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q34" t="n">
-        <v>466.2233328154397</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R34" t="n">
-        <v>84.56167017509823</v>
+        <v>81.68251716755651</v>
       </c>
       <c r="S34" t="n">
         <v>52.4</v>
@@ -6882,19 +6882,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U34" t="n">
-        <v>329.4820370429931</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V34" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W34" t="n">
-        <v>539.8143481886165</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X34" t="n">
-        <v>610.65513921281</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y34" t="n">
-        <v>641.8744398918423</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="35">
@@ -6928,16 +6928,16 @@
         <v>29.92</v>
       </c>
       <c r="J35" t="n">
-        <v>119.1959849731395</v>
+        <v>400.1800000000361</v>
       </c>
       <c r="K35" t="n">
-        <v>489.4559849731395</v>
+        <v>585.9767376382271</v>
       </c>
       <c r="L35" t="n">
-        <v>859.7159849731394</v>
+        <v>956.2367376382271</v>
       </c>
       <c r="M35" t="n">
-        <v>859.7159849731395</v>
+        <v>956.2367376382271</v>
       </c>
       <c r="N35" t="n">
         <v>1109.691587554807</v>
@@ -6983,25 +6983,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>875.5512958944987</v>
+        <v>908.8661950295065</v>
       </c>
       <c r="C36" t="n">
-        <v>510.8039095858933</v>
+        <v>544.1188087209011</v>
       </c>
       <c r="D36" t="n">
-        <v>510.8039095858933</v>
+        <v>544.1188087209011</v>
       </c>
       <c r="E36" t="n">
-        <v>164.6704780486078</v>
+        <v>544.1188087209011</v>
       </c>
       <c r="F36" t="n">
-        <v>29.92</v>
+        <v>544.1188087209011</v>
       </c>
       <c r="G36" t="n">
-        <v>29.92</v>
+        <v>544.1188087209011</v>
       </c>
       <c r="H36" t="n">
-        <v>29.92</v>
+        <v>216.2964031390387</v>
       </c>
       <c r="I36" t="n">
         <v>29.92</v>
@@ -7010,16 +7010,16 @@
         <v>29.92</v>
       </c>
       <c r="K36" t="n">
-        <v>52.38685509283023</v>
+        <v>345.3082935472136</v>
       </c>
       <c r="L36" t="n">
-        <v>243.3466092744054</v>
+        <v>715.5682935472497</v>
       </c>
       <c r="M36" t="n">
-        <v>527.4420010172646</v>
+        <v>999.663685290109</v>
       </c>
       <c r="N36" t="n">
-        <v>863.9779994927574</v>
+        <v>999.663685290109</v>
       </c>
       <c r="O36" t="n">
         <v>1234.237999492757</v>
@@ -7046,13 +7046,13 @@
         <v>1312.153197263404</v>
       </c>
       <c r="W36" t="n">
-        <v>1276.422749879739</v>
+        <v>934.3754194855892</v>
       </c>
       <c r="X36" t="n">
-        <v>1253.329073672277</v>
+        <v>911.281743278127</v>
       </c>
       <c r="Y36" t="n">
-        <v>875.5512958944987</v>
+        <v>908.8661950295065</v>
       </c>
     </row>
     <row r="37">
@@ -7062,28 +7062,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>461.4420370429931</v>
+        <v>279.6105510052051</v>
       </c>
       <c r="C37" t="n">
-        <v>584.4740428614289</v>
+        <v>402.6425568236409</v>
       </c>
       <c r="D37" t="n">
-        <v>584.4740428614289</v>
+        <v>402.6425568236409</v>
       </c>
       <c r="E37" t="n">
-        <v>584.4740428614289</v>
+        <v>402.6425568236409</v>
       </c>
       <c r="F37" t="n">
-        <v>705.8650154533643</v>
+        <v>524.0335294155764</v>
       </c>
       <c r="G37" t="n">
-        <v>856.9567665861512</v>
+        <v>524.0335294155764</v>
       </c>
       <c r="H37" t="n">
-        <v>1029.328544204565</v>
+        <v>696.4053070339903</v>
       </c>
       <c r="I37" t="n">
-        <v>1029.328544204565</v>
+        <v>696.4053070339903</v>
       </c>
       <c r="J37" t="n">
         <v>1066.665307034026</v>
@@ -7113,25 +7113,25 @@
         <v>29.92</v>
       </c>
       <c r="S37" t="n">
-        <v>29.92</v>
+        <v>75.61834706138623</v>
       </c>
       <c r="T37" t="n">
-        <v>217.8251070276573</v>
+        <v>131.5497599810116</v>
       </c>
       <c r="U37" t="n">
-        <v>461.4420370429931</v>
+        <v>131.5497599810116</v>
       </c>
       <c r="V37" t="n">
-        <v>461.4420370429931</v>
+        <v>131.5497599810116</v>
       </c>
       <c r="W37" t="n">
-        <v>461.4420370429931</v>
+        <v>131.5497599810116</v>
       </c>
       <c r="X37" t="n">
-        <v>461.4420370429931</v>
+        <v>279.6105510052051</v>
       </c>
       <c r="Y37" t="n">
-        <v>461.4420370429931</v>
+        <v>279.6105510052051</v>
       </c>
     </row>
     <row r="38">
@@ -7165,25 +7165,25 @@
         <v>29.92</v>
       </c>
       <c r="J38" t="n">
-        <v>400.1800000000451</v>
+        <v>400.1800000000631</v>
       </c>
       <c r="K38" t="n">
-        <v>585.976737638236</v>
+        <v>585.9767376382541</v>
       </c>
       <c r="L38" t="n">
-        <v>816.4740199497938</v>
+        <v>816.4740199498118</v>
       </c>
       <c r="M38" t="n">
-        <v>816.4740199497938</v>
+        <v>816.4740199498118</v>
       </c>
       <c r="N38" t="n">
-        <v>1109.691587554807</v>
+        <v>816.4740199498118</v>
       </c>
       <c r="O38" t="n">
-        <v>1286.24475964128</v>
+        <v>993.0271920362844</v>
       </c>
       <c r="P38" t="n">
-        <v>1496</v>
+        <v>1202.782432395005</v>
       </c>
       <c r="Q38" t="n">
         <v>1496</v>
@@ -7192,10 +7192,10 @@
         <v>1496</v>
       </c>
       <c r="S38" t="n">
-        <v>1434.457487638385</v>
+        <v>1431.123215102471</v>
       </c>
       <c r="T38" t="n">
-        <v>1249.38969024747</v>
+        <v>1246.055417711555</v>
       </c>
       <c r="U38" t="n">
         <v>994.7399262092307</v>
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>567.9197065942985</v>
+        <v>1242.588531239008</v>
       </c>
       <c r="C39" t="n">
-        <v>567.9197065942985</v>
+        <v>877.8411449304031</v>
       </c>
       <c r="D39" t="n">
-        <v>567.9197065942985</v>
+        <v>877.8411449304031</v>
       </c>
       <c r="E39" t="n">
-        <v>221.786275057013</v>
+        <v>877.8411449304031</v>
       </c>
       <c r="F39" t="n">
-        <v>221.786275057013</v>
+        <v>877.8411449304031</v>
       </c>
       <c r="G39" t="n">
-        <v>221.786275057013</v>
+        <v>549.6086806388755</v>
       </c>
       <c r="H39" t="n">
         <v>221.786275057013</v>
@@ -7250,13 +7250,13 @@
         <v>543.0996394772296</v>
       </c>
       <c r="L39" t="n">
-        <v>784.4390741634611</v>
+        <v>599.927050901758</v>
       </c>
       <c r="M39" t="n">
-        <v>1068.53446590632</v>
+        <v>884.0224426446173</v>
       </c>
       <c r="N39" t="n">
-        <v>1405.070464381813</v>
+        <v>1220.55844112011</v>
       </c>
       <c r="O39" t="n">
         <v>1451.197204214901</v>
@@ -7274,22 +7274,22 @@
         <v>1338.259295700009</v>
       </c>
       <c r="T39" t="n">
-        <v>960.4815179222317</v>
+        <v>1333.031068969912</v>
       </c>
       <c r="U39" t="n">
-        <v>646.8469210517435</v>
+        <v>1329.840739881101</v>
       </c>
       <c r="V39" t="n">
-        <v>629.1593784340464</v>
+        <v>1303.828203078756</v>
       </c>
       <c r="W39" t="n">
-        <v>593.4289310503813</v>
+        <v>1268.097755695091</v>
       </c>
       <c r="X39" t="n">
-        <v>570.3352548429191</v>
+        <v>1245.004079487629</v>
       </c>
       <c r="Y39" t="n">
-        <v>567.9197065942985</v>
+        <v>1242.588531239008</v>
       </c>
     </row>
     <row r="40">
@@ -7299,28 +7299,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>495.185325966367</v>
+        <v>432.4443723487209</v>
       </c>
       <c r="C40" t="n">
-        <v>495.185325966367</v>
+        <v>432.4443723487209</v>
       </c>
       <c r="D40" t="n">
-        <v>605.5344700913671</v>
+        <v>432.4443723487209</v>
       </c>
       <c r="E40" t="n">
-        <v>605.5344700913671</v>
+        <v>547.303276560134</v>
       </c>
       <c r="F40" t="n">
-        <v>605.5344700913671</v>
+        <v>547.303276560134</v>
       </c>
       <c r="G40" t="n">
-        <v>756.6262212241541</v>
+        <v>547.303276560134</v>
       </c>
       <c r="H40" t="n">
-        <v>928.997998842568</v>
+        <v>719.675054178548</v>
       </c>
       <c r="I40" t="n">
-        <v>928.997998842568</v>
+        <v>957.5411403277457</v>
       </c>
       <c r="J40" t="n">
         <v>1066.665307034026</v>
@@ -7350,25 +7350,25 @@
         <v>29.92</v>
       </c>
       <c r="S40" t="n">
-        <v>29.92</v>
+        <v>75.61834706138623</v>
       </c>
       <c r="T40" t="n">
-        <v>217.8251070276573</v>
+        <v>263.5234540890435</v>
       </c>
       <c r="U40" t="n">
-        <v>217.8251070276573</v>
+        <v>263.5234540890435</v>
       </c>
       <c r="V40" t="n">
-        <v>217.8251070276573</v>
+        <v>263.5234540890435</v>
       </c>
       <c r="W40" t="n">
-        <v>386.7460252873348</v>
+        <v>432.4443723487209</v>
       </c>
       <c r="X40" t="n">
-        <v>386.7460252873348</v>
+        <v>432.4443723487209</v>
       </c>
       <c r="Y40" t="n">
-        <v>495.185325966367</v>
+        <v>432.4443723487209</v>
       </c>
     </row>
     <row r="41">
@@ -7378,13 +7378,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>35.75301799595022</v>
+        <v>260.9325710572914</v>
       </c>
       <c r="C41" t="n">
-        <v>29.92</v>
+        <v>260.9325710572914</v>
       </c>
       <c r="D41" t="n">
-        <v>29.92</v>
+        <v>142.4081713200694</v>
       </c>
       <c r="E41" t="n">
         <v>29.92</v>
@@ -7402,25 +7402,25 @@
         <v>29.92</v>
       </c>
       <c r="J41" t="n">
-        <v>400.1800000000685</v>
+        <v>119.1959849731395</v>
       </c>
       <c r="K41" t="n">
-        <v>585.9767376382595</v>
+        <v>304.9927226113305</v>
       </c>
       <c r="L41" t="n">
-        <v>816.4740199498173</v>
+        <v>535.4900049228883</v>
       </c>
       <c r="M41" t="n">
-        <v>816.4740199498173</v>
+        <v>739.431587554699</v>
       </c>
       <c r="N41" t="n">
-        <v>816.4740199498173</v>
+        <v>739.431587554699</v>
       </c>
       <c r="O41" t="n">
-        <v>993.0271920362899</v>
+        <v>915.9847596411716</v>
       </c>
       <c r="P41" t="n">
-        <v>1202.78243239501</v>
+        <v>1125.739999999892</v>
       </c>
       <c r="Q41" t="n">
         <v>1496</v>
@@ -7429,25 +7429,25 @@
         <v>1496</v>
       </c>
       <c r="S41" t="n">
-        <v>1496</v>
+        <v>1334.368778629923</v>
       </c>
       <c r="T41" t="n">
-        <v>1496</v>
+        <v>1334.368778629923</v>
       </c>
       <c r="U41" t="n">
-        <v>1136.299730911256</v>
+        <v>974.668509541179</v>
       </c>
       <c r="V41" t="n">
-        <v>796.0461711467871</v>
+        <v>974.668509541179</v>
       </c>
       <c r="W41" t="n">
-        <v>447.184074196335</v>
+        <v>974.668509541179</v>
       </c>
       <c r="X41" t="n">
-        <v>447.184074196335</v>
+        <v>672.3636272576762</v>
       </c>
       <c r="Y41" t="n">
-        <v>226.661414920773</v>
+        <v>451.8409679821141</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>318.0281146697905</v>
+        <v>315.6172324016843</v>
       </c>
       <c r="C42" t="n">
-        <v>249.240324320781</v>
+        <v>246.8294420526749</v>
       </c>
       <c r="D42" t="n">
-        <v>193.7477112927986</v>
+        <v>191.3368290246924</v>
       </c>
       <c r="E42" t="n">
-        <v>143.5738757151091</v>
+        <v>141.1629934470029</v>
       </c>
       <c r="F42" t="n">
-        <v>96.46656022230415</v>
+        <v>94.05567795419802</v>
       </c>
       <c r="G42" t="n">
-        <v>64.19369189037258</v>
+        <v>61.78280962226644</v>
       </c>
       <c r="H42" t="n">
         <v>29.92</v>
@@ -7481,22 +7481,22 @@
         <v>29.92</v>
       </c>
       <c r="J42" t="n">
-        <v>134.7151459244344</v>
+        <v>227.711345930016</v>
       </c>
       <c r="K42" t="n">
-        <v>157.1820010172646</v>
+        <v>414.1790741634611</v>
       </c>
       <c r="L42" t="n">
-        <v>527.4420010172646</v>
+        <v>784.4390741634611</v>
       </c>
       <c r="M42" t="n">
-        <v>527.4420010172646</v>
+        <v>1068.53446590632</v>
       </c>
       <c r="N42" t="n">
-        <v>863.9779994927574</v>
+        <v>1405.070464381813</v>
       </c>
       <c r="O42" t="n">
-        <v>1234.237999492757</v>
+        <v>1451.197204214901</v>
       </c>
       <c r="P42" t="n">
         <v>1496</v>
@@ -7511,22 +7511,22 @@
         <v>1128.158285598999</v>
       </c>
       <c r="T42" t="n">
-        <v>1017.879553818396</v>
+        <v>1015.46867155029</v>
       </c>
       <c r="U42" t="n">
-        <v>909.6387196790806</v>
+        <v>907.2278374109744</v>
       </c>
       <c r="V42" t="n">
-        <v>786.9006720108785</v>
+        <v>784.4897897427722</v>
       </c>
       <c r="W42" t="n">
-        <v>646.1197195767082</v>
+        <v>643.708837308602</v>
       </c>
       <c r="X42" t="n">
-        <v>517.975538318741</v>
+        <v>515.5646560506348</v>
       </c>
       <c r="Y42" t="n">
-        <v>410.5094850196153</v>
+        <v>408.0986027515092</v>
       </c>
     </row>
     <row r="43">
@@ -7572,19 +7572,19 @@
         <v>1163.052803794637</v>
       </c>
       <c r="N43" t="n">
-        <v>1163.052803794637</v>
+        <v>984.3546982875536</v>
       </c>
       <c r="O43" t="n">
-        <v>1161.48146711209</v>
+        <v>843.8998519932802</v>
       </c>
       <c r="P43" t="n">
         <v>843.8998519932802</v>
       </c>
       <c r="Q43" t="n">
-        <v>466.1220742155024</v>
+        <v>466.1220742155023</v>
       </c>
       <c r="R43" t="n">
-        <v>88.34429643772452</v>
+        <v>88.34429643772449</v>
       </c>
       <c r="S43" t="n">
         <v>29.92</v>
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>306.4995292755997</v>
+        <v>396.9876847372074</v>
       </c>
       <c r="C44" t="n">
-        <v>148.444399737222</v>
+        <v>396.9876847372074</v>
       </c>
       <c r="D44" t="n">
-        <v>29.92</v>
+        <v>354.2347265621671</v>
       </c>
       <c r="E44" t="n">
-        <v>29.92</v>
+        <v>354.2347265621671</v>
       </c>
       <c r="F44" t="n">
-        <v>29.92</v>
+        <v>241.2148995843773</v>
       </c>
       <c r="G44" t="n">
-        <v>29.92</v>
+        <v>130.8290456423631</v>
       </c>
       <c r="H44" t="n">
         <v>29.92</v>
@@ -7651,13 +7651,13 @@
         <v>535.4900049228884</v>
       </c>
       <c r="N44" t="n">
-        <v>905.7500049230397</v>
+        <v>535.4900049228884</v>
       </c>
       <c r="O44" t="n">
-        <v>1082.303177009512</v>
+        <v>905.7500049230937</v>
       </c>
       <c r="P44" t="n">
-        <v>1292.058417368233</v>
+        <v>1125.739999999795</v>
       </c>
       <c r="Q44" t="n">
         <v>1496</v>
@@ -7669,22 +7669,22 @@
         <v>1326.072710051966</v>
       </c>
       <c r="T44" t="n">
-        <v>1035.954407610545</v>
+        <v>1326.072710051966</v>
       </c>
       <c r="U44" t="n">
-        <v>676.254138521801</v>
+        <v>966.3724409632214</v>
       </c>
       <c r="V44" t="n">
-        <v>676.254138521801</v>
+        <v>966.3724409632214</v>
       </c>
       <c r="W44" t="n">
-        <v>676.254138521801</v>
+        <v>617.5103440127693</v>
       </c>
       <c r="X44" t="n">
-        <v>373.9492562382982</v>
+        <v>617.5103440127693</v>
       </c>
       <c r="Y44" t="n">
-        <v>373.9492562382982</v>
+        <v>396.9876847372074</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>318.0281146697906</v>
+        <v>315.6172324016843</v>
       </c>
       <c r="C45" t="n">
-        <v>249.2403243207812</v>
+        <v>246.8294420526749</v>
       </c>
       <c r="D45" t="n">
-        <v>193.7477112927987</v>
+        <v>191.3368290246924</v>
       </c>
       <c r="E45" t="n">
-        <v>143.5738757151092</v>
+        <v>141.1629934470029</v>
       </c>
       <c r="F45" t="n">
-        <v>96.46656022230427</v>
+        <v>94.05567795419802</v>
       </c>
       <c r="G45" t="n">
-        <v>64.19369189037269</v>
+        <v>61.78280962226644</v>
       </c>
       <c r="H45" t="n">
         <v>29.92</v>
@@ -7718,19 +7718,19 @@
         <v>29.92</v>
       </c>
       <c r="J45" t="n">
-        <v>227.711345930016</v>
+        <v>187.1557526566573</v>
       </c>
       <c r="K45" t="n">
-        <v>543.0996394772296</v>
+        <v>209.6226077494875</v>
       </c>
       <c r="L45" t="n">
-        <v>599.927050901758</v>
+        <v>579.8826077496929</v>
       </c>
       <c r="M45" t="n">
-        <v>599.927050901758</v>
+        <v>863.977999492552</v>
       </c>
       <c r="N45" t="n">
-        <v>936.4630493772507</v>
+        <v>863.977999492552</v>
       </c>
       <c r="O45" t="n">
         <v>1234.237999492757</v>
@@ -7739,31 +7739,31 @@
         <v>1496</v>
       </c>
       <c r="Q45" t="n">
-        <v>1496</v>
+        <v>1493.589117731894</v>
       </c>
       <c r="R45" t="n">
-        <v>1288.664660634723</v>
+        <v>1286.253778366616</v>
       </c>
       <c r="S45" t="n">
-        <v>1128.158285598999</v>
+        <v>1125.747403330893</v>
       </c>
       <c r="T45" t="n">
-        <v>1017.879553818397</v>
+        <v>1015.46867155029</v>
       </c>
       <c r="U45" t="n">
-        <v>909.6387196790807</v>
+        <v>907.2278374109744</v>
       </c>
       <c r="V45" t="n">
-        <v>786.9006720108786</v>
+        <v>784.4897897427722</v>
       </c>
       <c r="W45" t="n">
-        <v>646.1197195767083</v>
+        <v>643.708837308602</v>
       </c>
       <c r="X45" t="n">
-        <v>517.9755383187411</v>
+        <v>515.5646560506348</v>
       </c>
       <c r="Y45" t="n">
-        <v>410.5094850196155</v>
+        <v>408.0986027515092</v>
       </c>
     </row>
     <row r="46">
@@ -7803,22 +7803,22 @@
         <v>1163.052803794637</v>
       </c>
       <c r="L46" t="n">
-        <v>1163.052803794637</v>
+        <v>1130.57247066623</v>
       </c>
       <c r="M46" t="n">
-        <v>1163.052803794637</v>
+        <v>1130.57247066623</v>
       </c>
       <c r="N46" t="n">
-        <v>1163.052803794637</v>
+        <v>951.8743651591461</v>
       </c>
       <c r="O46" t="n">
-        <v>1161.48146711209</v>
+        <v>783.7036893345216</v>
       </c>
       <c r="P46" t="n">
-        <v>843.8998519932802</v>
+        <v>466.1220742157118</v>
       </c>
       <c r="Q46" t="n">
-        <v>466.1220742155023</v>
+        <v>466.1220742157118</v>
       </c>
       <c r="R46" t="n">
         <v>88.34429643772449</v>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7976,16 +7976,16 @@
         <v>846.2608914614127</v>
       </c>
       <c r="N2" t="n">
-        <v>404.0826666125488</v>
+        <v>587.423942175285</v>
       </c>
       <c r="O2" t="n">
-        <v>375.1590153027356</v>
+        <v>1.159015302735668</v>
       </c>
       <c r="P2" t="n">
-        <v>315.3213213472141</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>370.5618244726559</v>
+        <v>502.5418702571336</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,19 +8201,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>374.2405037325275</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K5" t="n">
-        <v>248.0502805878619</v>
+        <v>321.8400703517588</v>
       </c>
       <c r="L5" t="n">
-        <v>309.2909949748744</v>
+        <v>309.2909949748743</v>
       </c>
       <c r="M5" t="n">
         <v>472.2608914614128</v>
       </c>
       <c r="N5" t="n">
-        <v>404.0826666125488</v>
+        <v>704.2928768486519</v>
       </c>
       <c r="O5" t="n">
         <v>1.159015302735668</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>467.3265276381908</v>
+        <v>467.326527638191</v>
       </c>
       <c r="L11" t="n">
-        <v>422.1744623115578</v>
+        <v>422.1744623115576</v>
       </c>
       <c r="M11" t="n">
-        <v>658.0411930141927</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N11" t="n">
-        <v>213.993772140187</v>
+        <v>868.993772140187</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.49857879984722</v>
+        <v>161.6456521146628</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8918,22 +8918,22 @@
         <v>467.326527638191</v>
       </c>
       <c r="L14" t="n">
-        <v>179.8420213169702</v>
+        <v>422.1744623115576</v>
       </c>
       <c r="M14" t="n">
-        <v>285.1988562855334</v>
+        <v>940.1988562855347</v>
       </c>
       <c r="N14" t="n">
-        <v>213.993772140187</v>
+        <v>362.1408454550016</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>443.126019839677</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9155,16 +9155,16 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>382.6480632645636</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>940.198856285534</v>
+        <v>940.1988562855356</v>
       </c>
       <c r="N17" t="n">
-        <v>868.9937721401875</v>
+        <v>868.9937721401893</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>382.6480632645601</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -9389,16 +9389,16 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>382.6480632645636</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>382.6480632645565</v>
       </c>
       <c r="M20" t="n">
-        <v>940.198856285534</v>
+        <v>940.1988562855374</v>
       </c>
       <c r="N20" t="n">
-        <v>868.9937721401875</v>
+        <v>868.9937721401911</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9632,19 +9632,19 @@
         <v>422.1744623115576</v>
       </c>
       <c r="M23" t="n">
-        <v>433.3459296003487</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N23" t="n">
-        <v>868.9937721401875</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>476.6634625389205</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>13.49857879984722</v>
+        <v>339.9821895757423</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,25 +9863,25 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>467.326527638191</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>422.1744623115576</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>940.1988562855336</v>
+        <v>940.1988562855408</v>
       </c>
       <c r="N26" t="n">
-        <v>362.1408454550025</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>476.6634625389239</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>13.49857879984722</v>
+        <v>574.4831795254802</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,25 +10097,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>467.326527638191</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>422.1744623115576</v>
       </c>
       <c r="M29" t="n">
-        <v>940.1988562855363</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N29" t="n">
-        <v>213.993772140187</v>
+        <v>574.014825615317</v>
       </c>
       <c r="O29" t="n">
-        <v>164.2173068387257</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>443.1260198396793</v>
+        <v>443.1260198396859</v>
       </c>
       <c r="Q29" t="n">
         <v>13.49857879984722</v>
@@ -10343,13 +10343,13 @@
         <v>422.1744623115576</v>
       </c>
       <c r="M32" t="n">
-        <v>433.3459296003455</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N32" t="n">
-        <v>868.9937721401907</v>
+        <v>868.9937721402052</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>148.1470733147974</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -10571,19 +10571,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>283.8222374009056</v>
       </c>
       <c r="K35" t="n">
-        <v>186.326527638191</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>141.1744623115577</v>
+        <v>141.1744623115578</v>
       </c>
       <c r="M35" t="n">
         <v>285.1988562855334</v>
       </c>
       <c r="N35" t="n">
-        <v>466.494380808538</v>
+        <v>368.9986710458234</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10653,19 +10653,19 @@
         <v>27.675503614641</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L36" t="n">
-        <v>135.4872149061079</v>
+        <v>316.5985743186947</v>
       </c>
       <c r="M36" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N36" t="n">
-        <v>485.4085271713503</v>
+        <v>145.473175175903</v>
       </c>
       <c r="O36" t="n">
-        <v>327.4073335019309</v>
+        <v>190.3510852217777</v>
       </c>
       <c r="P36" t="n">
         <v>219.1507118405495</v>
@@ -10808,7 +10808,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>283.8222374009147</v>
+        <v>283.8222374009329</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -10820,7 +10820,7 @@
         <v>285.1988562855334</v>
       </c>
       <c r="N38" t="n">
-        <v>510.173133357372</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>13.49857879984722</v>
+        <v>309.677940017014</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10893,7 +10893,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>186.3757810724275</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>471.6948204301074</v>
@@ -10902,7 +10902,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>186.3757810724272</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -11045,7 +11045,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>283.8222374009384</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -11054,7 +11054,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>285.1988562855334</v>
+        <v>491.200454903524</v>
       </c>
       <c r="N41" t="n">
         <v>213.993772140187</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>309.6779400170085</v>
+        <v>387.4985787999565</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11124,25 +11124,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>133.5291863665949</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>165.6574476167827</v>
       </c>
       <c r="L42" t="n">
         <v>316.5985743186583</v>
       </c>
       <c r="M42" t="n">
-        <v>184.7297782656032</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N42" t="n">
         <v>485.4085271713503</v>
       </c>
       <c r="O42" t="n">
-        <v>327.4073335019309</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>219.1507118405495</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>17.27519534353338</v>
@@ -11294,16 +11294,16 @@
         <v>285.1988562855334</v>
       </c>
       <c r="N44" t="n">
-        <v>587.9937721403398</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>195.663462539124</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>10.33813607876831</v>
       </c>
       <c r="Q44" t="n">
-        <v>219.5001774177942</v>
+        <v>387.4985788000547</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11361,22 +11361,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>227.4647419277884</v>
+        <v>186.4994961971231</v>
       </c>
       <c r="K45" t="n">
-        <v>295.8802408630135</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>316.5985743188657</v>
       </c>
       <c r="M45" t="n">
-        <v>184.7297782656032</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N45" t="n">
-        <v>485.4085271713503</v>
+        <v>145.473175175903</v>
       </c>
       <c r="O45" t="n">
-        <v>254.1901113963821</v>
+        <v>327.4073335021384</v>
       </c>
       <c r="P45" t="n">
         <v>219.1507118405495</v>
@@ -23274,10 +23274,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.696084996495216</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6960849964949603</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -23411,7 +23411,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2.850361477466352</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -23420,7 +23420,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -23463,7 +23463,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6960849964949034</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -23514,7 +23514,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>0.6960849964949603</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -23669,7 +23669,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.850361477464521</v>
+        <v>2.85036147746635</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23897,7 +23897,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.850361477466265</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23949,10 +23949,10 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.696084996494875</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6960849964949034</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.850361477464553</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24186,7 +24186,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.696084996494875</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.696084996495216</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.850361477465871</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24417,7 +24417,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.6960849964949034</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -24426,7 +24426,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6960849964948608</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>2.850361477466352</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -24611,7 +24611,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.850361477466379</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -24660,7 +24660,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.696084996494875</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -24696,7 +24696,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.696084996495216</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -24848,10 +24848,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="R31" t="n">
-        <v>2.850361477466265</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -24900,7 +24900,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>0.6960849963935658</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -24939,7 +24939,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0.6960849964950739</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -25079,7 +25079,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>2.850361477466521</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -25091,7 +25091,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25407,13 +25407,13 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
         <v>3.300929810555573</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -25596,13 +25596,13 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>150.6998904270032</v>
+        <v>156.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>117.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>111.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>111.8896287080119</v>
@@ -25611,7 +25611,7 @@
         <v>109.2819954025941</v>
       </c>
       <c r="H41" t="n">
-        <v>99.89995518593946</v>
+        <v>99.89995518593948</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25644,7 +25644,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>168.2280170485541</v>
+        <v>8.213107892178158</v>
       </c>
       <c r="T41" t="n">
         <v>287.2171194170061</v>
@@ -25653,13 +25653,13 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>336.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>345.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>299.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -25781,25 +25781,25 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>32.15552979712345</v>
+        <v>32.15552979712344</v>
       </c>
       <c r="M43" t="n">
         <v>123.8909392714024</v>
       </c>
       <c r="N43" t="n">
-        <v>176.9111244520127</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>252.3470555173917</v>
+        <v>114.8523810017827</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>314.4057989676218</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.422266425597968</v>
+        <v>3.422266425597996</v>
       </c>
       <c r="R43" t="n">
-        <v>29.84504601393797</v>
+        <v>29.84504601393795</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -25830,25 +25830,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>122.2240832625029</v>
+        <v>188.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>156.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>75.01372714655994</v>
       </c>
       <c r="E44" t="n">
         <v>111.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>111.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>109.2819954025941</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>99.89995518593948</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25884,7 +25884,7 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>287.2171194170061</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -25893,13 +25893,13 @@
         <v>336.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>345.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>299.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>218.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -26018,25 +26018,25 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>32.15552979712344</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>123.8909392714024</v>
       </c>
       <c r="N46" t="n">
-        <v>176.9111244520127</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>252.3470555173917</v>
+        <v>87.41370976673505</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.422266425597996</v>
+        <v>377.422266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>29.84504601393795</v>
+        <v>29.84504601373047</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1101954.91029102</v>
+        <v>1101954.910291021</v>
       </c>
       <c r="C2" t="n">
         <v>1101954.91029102</v>
@@ -26293,13 +26293,13 @@
         <v>1101846.570379988</v>
       </c>
       <c r="J2" t="n">
+        <v>1101846.570379987</v>
+      </c>
+      <c r="K2" t="n">
         <v>1101846.570379988</v>
       </c>
-      <c r="K2" t="n">
-        <v>1101846.570379989</v>
-      </c>
       <c r="L2" t="n">
-        <v>1101846.570379988</v>
+        <v>1101846.570379995</v>
       </c>
       <c r="M2" t="n">
         <v>1101725.000529716</v>
@@ -26308,10 +26308,10 @@
         <v>1101725.000529716</v>
       </c>
       <c r="O2" t="n">
-        <v>987610.1574599879</v>
+        <v>987610.1574599878</v>
       </c>
       <c r="P2" t="n">
-        <v>987610.1574599879</v>
+        <v>987610.1574599881</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602419.1762101187</v>
+        <v>602219.8615549037</v>
       </c>
       <c r="C4" t="n">
-        <v>600410.25402263</v>
+        <v>600210.9393674152</v>
       </c>
       <c r="D4" t="n">
-        <v>598398.6066068059</v>
+        <v>598199.2919515911</v>
       </c>
       <c r="E4" t="n">
-        <v>508463.6174685808</v>
+        <v>508269.4590428486</v>
       </c>
       <c r="F4" t="n">
-        <v>506794.9519687437</v>
+        <v>506600.7935430115</v>
       </c>
       <c r="G4" t="n">
-        <v>505123.9837731232</v>
+        <v>504929.8253473911</v>
       </c>
       <c r="H4" t="n">
-        <v>503450.6963689994</v>
+        <v>503256.5379432672</v>
       </c>
       <c r="I4" t="n">
-        <v>501775.0730285004</v>
+        <v>501580.9146027682</v>
       </c>
       <c r="J4" t="n">
-        <v>500097.0968045217</v>
+        <v>499902.9383787895</v>
       </c>
       <c r="K4" t="n">
-        <v>498416.7505265499</v>
+        <v>498222.5921008177</v>
       </c>
       <c r="L4" t="n">
-        <v>496734.0167963753</v>
+        <v>496539.8583706476</v>
       </c>
       <c r="M4" t="n">
-        <v>522490.4615842147</v>
+        <v>522371.0444804642</v>
       </c>
       <c r="N4" t="n">
-        <v>520523.3308731494</v>
+        <v>520403.913769399</v>
       </c>
       <c r="O4" t="n">
-        <v>447790.3844155932</v>
+        <v>447670.9673118427</v>
       </c>
       <c r="P4" t="n">
-        <v>446122.6297523478</v>
+        <v>446003.2126485973</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>209847.3340809016</v>
+        <v>210046.6487361169</v>
       </c>
       <c r="C6" t="n">
-        <v>442954.2562683902</v>
+        <v>443153.5709236051</v>
       </c>
       <c r="D6" t="n">
-        <v>444965.903684215</v>
+        <v>445165.2183394294</v>
       </c>
       <c r="E6" t="n">
-        <v>-93746.65808859273</v>
+        <v>-93552.49966286073</v>
       </c>
       <c r="F6" t="n">
-        <v>520409.0074112443</v>
+        <v>520603.1658369765</v>
       </c>
       <c r="G6" t="n">
-        <v>522079.9756068646</v>
+        <v>522274.134032597</v>
       </c>
       <c r="H6" t="n">
-        <v>523753.2630109884</v>
+        <v>523947.421436721</v>
       </c>
       <c r="I6" t="n">
-        <v>525428.8863514874</v>
+        <v>525623.0447772196</v>
       </c>
       <c r="J6" t="n">
-        <v>140258.8625754661</v>
+        <v>140453.0210011978</v>
       </c>
       <c r="K6" t="n">
-        <v>528787.2088534385</v>
+        <v>528981.3672791701</v>
       </c>
       <c r="L6" t="n">
-        <v>530469.9425836126</v>
+        <v>530664.1010093474</v>
       </c>
       <c r="M6" t="n">
-        <v>452719.3459455014</v>
+        <v>452838.7630492515</v>
       </c>
       <c r="N6" t="n">
-        <v>517086.4766565664</v>
+        <v>517205.8937603165</v>
       </c>
       <c r="O6" t="n">
-        <v>312447.7560443947</v>
+        <v>312567.1731481451</v>
       </c>
       <c r="P6" t="n">
-        <v>486115.5107076401</v>
+        <v>486234.9278113908</v>
       </c>
     </row>
   </sheetData>
@@ -26999,7 +26999,7 @@
         <v>319</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
@@ -27484,13 +27484,13 @@
         <v>225.120779732817</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>398.2013121321733</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
       </c>
       <c r="U2" t="n">
-        <v>398.2013121321734</v>
+        <v>400</v>
       </c>
       <c r="V2" t="n">
         <v>400</v>
@@ -27515,7 +27515,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>103.6184651146505</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27527,10 +27527,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27572,13 +27572,13 @@
         <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>400</v>
+        <v>40.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>229.534809722118</v>
+        <v>45.86273944538755</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27594,13 +27594,13 @@
         <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>376.2055487784801</v>
       </c>
       <c r="F4" t="n">
         <v>274.3828559677419</v>
@@ -27612,10 +27612,10 @@
         <v>227.1357818393235</v>
       </c>
       <c r="I4" t="n">
-        <v>251.1925171289639</v>
+        <v>171.1020457840527</v>
       </c>
       <c r="J4" t="n">
-        <v>22.26478490148153</v>
+        <v>396.2647849014816</v>
       </c>
       <c r="K4" t="n">
         <v>267.1509377355693</v>
@@ -27642,22 +27642,22 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
+        <v>359.1680042930194</v>
+      </c>
+      <c r="T4" t="n">
         <v>400</v>
       </c>
-      <c r="T4" t="n">
-        <v>209.2386648669134</v>
-      </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9483584875727</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
         <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
         <v>400</v>
@@ -27688,10 +27688,10 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>398.2013121321735</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.2726973711268</v>
+        <v>132.4740095033003</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27752,16 +27752,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>210.6652859026073</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>325.5201396486123</v>
@@ -27797,7 +27797,7 @@
         <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
-        <v>400</v>
+        <v>159.6519859716246</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27809,10 +27809,10 @@
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>400</v>
+        <v>40.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>400</v>
+        <v>167.0943807341541</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
@@ -27834,31 +27834,31 @@
         <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>244.8599384153005</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>277.5918790081056</v>
       </c>
       <c r="I7" t="n">
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>124.0957664680556</v>
+        <v>396.2647849014816</v>
       </c>
       <c r="K7" t="n">
         <v>267.1509377355693</v>
       </c>
       <c r="L7" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,7 +27879,7 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>359.1680042930194</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
         <v>209.2386648669134</v>
@@ -27888,7 +27888,7 @@
         <v>150.9483584875727</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W7" t="n">
         <v>226.3728098387097</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>134.2726973711268</v>
+        <v>132.4740095033003</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27958,7 +27958,7 @@
         <v>225.120779732817</v>
       </c>
       <c r="S8" t="n">
-        <v>398.2013121321733</v>
+        <v>400</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27995,7 +27995,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28007,7 +28007,7 @@
         <v>330.0491815260438</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28043,19 +28043,19 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
+        <v>26.1959257979226</v>
+      </c>
+      <c r="V9" t="n">
         <v>400</v>
       </c>
-      <c r="V9" t="n">
-        <v>283.9291311192114</v>
-      </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>150.6337204058187</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>25.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>317.0746988257476</v>
       </c>
       <c r="C10" t="n">
         <v>272.7252466480447</v>
@@ -28074,7 +28074,7 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
         <v>274.3828559677419</v>
@@ -28083,7 +28083,7 @@
         <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I10" t="n">
         <v>400</v>
@@ -28092,10 +28092,10 @@
         <v>396.2647849014816</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L10" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28119,16 +28119,16 @@
         <v>400</v>
       </c>
       <c r="T10" t="n">
+        <v>209.2386648669134</v>
+      </c>
+      <c r="U10" t="n">
         <v>400</v>
-      </c>
-      <c r="U10" t="n">
-        <v>222.3341636257032</v>
       </c>
       <c r="V10" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
         <v>247.4436454301076</v>
@@ -28238,13 +28238,13 @@
         <v>319</v>
       </c>
       <c r="G12" t="n">
-        <v>319</v>
+        <v>96.05772723972419</v>
       </c>
       <c r="H12" t="n">
         <v>319</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28271,7 +28271,7 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R12" t="n">
-        <v>286.0053395461672</v>
+        <v>319</v>
       </c>
       <c r="S12" t="n">
         <v>319</v>
@@ -28463,10 +28463,10 @@
         <v>319</v>
       </c>
       <c r="C15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>319</v>
@@ -28475,13 +28475,13 @@
         <v>319</v>
       </c>
       <c r="G15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>319</v>
       </c>
       <c r="I15" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28511,10 +28511,10 @@
         <v>319</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>286.0053395461672</v>
       </c>
       <c r="T15" t="n">
-        <v>96.05772723972433</v>
+        <v>319</v>
       </c>
       <c r="U15" t="n">
         <v>319</v>
@@ -28523,13 +28523,13 @@
         <v>319</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="X15" t="n">
         <v>319</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16">
@@ -28542,7 +28542,7 @@
         <v>319</v>
       </c>
       <c r="C16" t="n">
-        <v>319.0000000000021</v>
+        <v>319</v>
       </c>
       <c r="D16" t="n">
         <v>319</v>
@@ -28697,16 +28697,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>96.05772723972439</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D18" t="n">
-        <v>96.05772723972461</v>
+        <v>319</v>
       </c>
       <c r="E18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>319</v>
@@ -28754,10 +28754,10 @@
         <v>319</v>
       </c>
       <c r="U18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>319</v>
@@ -28766,7 +28766,7 @@
         <v>319</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19">
@@ -28934,22 +28934,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>96.0577272397245</v>
+        <v>319</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>96.05772723972427</v>
       </c>
       <c r="E21" t="n">
         <v>319</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>319</v>
@@ -28991,7 +28991,7 @@
         <v>319</v>
       </c>
       <c r="U21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>319</v>
@@ -29000,7 +29000,7 @@
         <v>319</v>
       </c>
       <c r="X21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>319</v>
@@ -29034,7 +29034,7 @@
         <v>319</v>
       </c>
       <c r="I22" t="n">
-        <v>319.0000000000016</v>
+        <v>319</v>
       </c>
       <c r="J22" t="n">
         <v>319</v>
@@ -29171,19 +29171,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>96.0577272397245</v>
+        <v>319</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G24" t="n">
         <v>319</v>
@@ -29219,7 +29219,7 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>319</v>
@@ -29231,7 +29231,7 @@
         <v>319</v>
       </c>
       <c r="V24" t="n">
-        <v>319</v>
+        <v>96.0577272397245</v>
       </c>
       <c r="W24" t="n">
         <v>319</v>
@@ -29265,7 +29265,7 @@
         <v>319</v>
       </c>
       <c r="G25" t="n">
-        <v>319.0000000000006</v>
+        <v>319</v>
       </c>
       <c r="H25" t="n">
         <v>319</v>
@@ -29408,16 +29408,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D27" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>319</v>
@@ -29471,13 +29471,13 @@
         <v>319</v>
       </c>
       <c r="W27" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>96.05772723972456</v>
+        <v>319</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>96.05772723972444</v>
       </c>
     </row>
     <row r="28">
@@ -29648,7 +29648,7 @@
         <v>319</v>
       </c>
       <c r="C30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>319</v>
@@ -29657,7 +29657,7 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G30" t="n">
         <v>319</v>
@@ -29666,7 +29666,7 @@
         <v>319</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29693,19 +29693,19 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R30" t="n">
-        <v>286.0053395461676</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>319</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="U30" t="n">
         <v>319</v>
       </c>
       <c r="V30" t="n">
-        <v>319</v>
+        <v>96.05772723972427</v>
       </c>
       <c r="W30" t="n">
         <v>319</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>158.200955612214</v>
+        <v>158.2009556123174</v>
       </c>
       <c r="S32" t="n">
         <v>319</v>
@@ -29891,7 +29891,7 @@
         <v>319</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -29933,22 +29933,22 @@
         <v>319</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>96.05772723972444</v>
       </c>
       <c r="T33" t="n">
-        <v>96.05772723972456</v>
+        <v>319</v>
       </c>
       <c r="U33" t="n">
         <v>319</v>
       </c>
       <c r="V33" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
         <v>319</v>
       </c>
       <c r="X33" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>319</v>
@@ -30128,19 +30128,19 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>206.2332690697551</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
         <v>324.9501396486123</v>
       </c>
       <c r="H36" t="n">
-        <v>324.5441815260438</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>189.9476123064429</v>
+        <v>5.434973198794552</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30182,13 +30182,13 @@
         <v>397</v>
       </c>
       <c r="W36" t="n">
-        <v>397</v>
+        <v>58.37314290979211</v>
       </c>
       <c r="X36" t="n">
         <v>397</v>
       </c>
       <c r="Y36" t="n">
-        <v>25.39139276613435</v>
+        <v>397</v>
       </c>
     </row>
     <row r="37">
@@ -30213,7 +30213,7 @@
         <v>397</v>
       </c>
       <c r="G37" t="n">
-        <v>397</v>
+        <v>244.3820695628415</v>
       </c>
       <c r="H37" t="n">
         <v>397</v>
@@ -30222,7 +30222,7 @@
         <v>156.7312261119215</v>
       </c>
       <c r="J37" t="n">
-        <v>26.19335888056986</v>
+        <v>362.4794570326655</v>
       </c>
       <c r="K37" t="n">
         <v>211.6312656044217</v>
@@ -30249,13 +30249,13 @@
         <v>397</v>
       </c>
       <c r="S37" t="n">
-        <v>350.8400534733473</v>
+        <v>397</v>
       </c>
       <c r="T37" t="n">
-        <v>397</v>
+        <v>263.6932382747152</v>
       </c>
       <c r="U37" t="n">
-        <v>397</v>
+        <v>150.9222929138022</v>
       </c>
       <c r="V37" t="n">
         <v>199.1703102162162</v>
@@ -30264,7 +30264,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X37" t="n">
-        <v>247.4436454301076</v>
+        <v>397</v>
       </c>
       <c r="Y37" t="n">
         <v>287.4653528494624</v>
@@ -30359,22 +30359,22 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>324.9501396486123</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>324.5441815260438</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -30410,13 +30410,13 @@
         <v>397</v>
       </c>
       <c r="T39" t="n">
-        <v>28.17594446279683</v>
+        <v>397</v>
       </c>
       <c r="U39" t="n">
-        <v>89.66017489613927</v>
+        <v>397</v>
       </c>
       <c r="V39" t="n">
-        <v>397</v>
+        <v>388.758255757199</v>
       </c>
       <c r="W39" t="n">
         <v>397</v>
@@ -30441,25 +30441,25 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D40" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E40" t="n">
         <v>397</v>
-      </c>
-      <c r="E40" t="n">
-        <v>280.9809048369565</v>
       </c>
       <c r="F40" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G40" t="n">
-        <v>397</v>
+        <v>244.3820695628415</v>
       </c>
       <c r="H40" t="n">
         <v>397</v>
       </c>
       <c r="I40" t="n">
-        <v>156.7312261119215</v>
+        <v>397</v>
       </c>
       <c r="J40" t="n">
-        <v>127.5373440947083</v>
+        <v>98.70588804907433</v>
       </c>
       <c r="K40" t="n">
         <v>211.6312656044217</v>
@@ -30486,7 +30486,7 @@
         <v>397</v>
       </c>
       <c r="S40" t="n">
-        <v>350.8400534733473</v>
+        <v>397</v>
       </c>
       <c r="T40" t="n">
         <v>397</v>
@@ -30504,7 +30504,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y40" t="n">
-        <v>397</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="41">
@@ -30611,7 +30611,7 @@
         <v>293</v>
       </c>
       <c r="H42" t="n">
-        <v>290.6132265545749</v>
+        <v>293</v>
       </c>
       <c r="I42" t="n">
         <v>189.9476123064429</v>
@@ -30647,7 +30647,7 @@
         <v>293</v>
       </c>
       <c r="T42" t="n">
-        <v>293</v>
+        <v>290.6132265545748</v>
       </c>
       <c r="U42" t="n">
         <v>293</v>
@@ -30848,7 +30848,7 @@
         <v>293</v>
       </c>
       <c r="H45" t="n">
-        <v>290.6132265545748</v>
+        <v>293</v>
       </c>
       <c r="I45" t="n">
         <v>189.9476123064429</v>
@@ -30875,7 +30875,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>72.31352924142297</v>
+        <v>69.92675579599782</v>
       </c>
       <c r="R45" t="n">
         <v>293</v>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K2" t="n">
-        <v>52.1599296482412</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512562</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M2" t="n">
         <v>374</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>183.3412755627362</v>
       </c>
       <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>58.67867865278593</v>
+      </c>
+      <c r="Q2" t="n">
         <v>374</v>
-      </c>
-      <c r="P2" t="n">
-        <v>374</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>242.0199542155222</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34880,13 +34880,13 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>95.22464394152357</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -34898,10 +34898,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>80.09047134491121</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34928,22 +34928,22 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>190.7613351330866</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
         <v>112.5346471505376</v>
@@ -34980,19 +34980,19 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>374</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
+        <v>373.9999999999999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>300.2102102361031</v>
-      </c>
-      <c r="L5" t="n">
-        <v>374</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -35120,31 +35120,31 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>155.1400615846995</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>172.8642181606765</v>
+        <v>50.45609716878207</v>
       </c>
       <c r="I7" t="n">
         <v>228.8979542159473</v>
       </c>
       <c r="J7" t="n">
-        <v>101.830981566574</v>
+        <v>374</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.798404629106074</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,7 +35165,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -35174,7 +35174,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>29.960898488669</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -35360,7 +35360,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -35369,7 +35369,7 @@
         <v>155.1400615846995</v>
       </c>
       <c r="H10" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>228.8979542159473</v>
@@ -35378,10 +35378,10 @@
         <v>374</v>
       </c>
       <c r="K10" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35405,16 +35405,16 @@
         <v>40.83199570698065</v>
       </c>
       <c r="T10" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>71.38580513813049</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -35454,19 +35454,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>520.4824991852875</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K11" t="n">
+        <v>655</v>
+      </c>
+      <c r="L11" t="n">
         <v>654.9999999999999</v>
       </c>
-      <c r="L11" t="n">
-        <v>655</v>
-      </c>
       <c r="M11" t="n">
-        <v>372.8423367286592</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>655.0000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>178.3365374610834</v>
@@ -35475,7 +35475,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>148.1470733148155</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35697,22 +35697,22 @@
         <v>655</v>
       </c>
       <c r="L14" t="n">
-        <v>412.6675590054125</v>
+        <v>654.9999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>655.0000000000013</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>148.1470733148146</v>
       </c>
       <c r="O14" t="n">
         <v>178.3365374610834</v>
       </c>
       <c r="P14" t="n">
-        <v>655.0000000000006</v>
+        <v>211.8739801603236</v>
       </c>
       <c r="Q14" t="n">
-        <v>602.3534944697265</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35828,7 +35828,7 @@
         <v>31.88619966292134</v>
       </c>
       <c r="C16" t="n">
-        <v>46.27475335195742</v>
+        <v>46.27475335195533</v>
       </c>
       <c r="D16" t="n">
         <v>33.46378194444452</v>
@@ -35852,7 +35852,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K16" t="n">
-        <v>107.3687343955783</v>
+        <v>107.3687343955782</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35934,16 +35934,16 @@
         <v>187.673472361809</v>
       </c>
       <c r="L17" t="n">
-        <v>615.4736009530058</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M17" t="n">
-        <v>655.0000000000006</v>
+        <v>655.0000000000022</v>
       </c>
       <c r="N17" t="n">
-        <v>655.0000000000006</v>
+        <v>655.0000000000022</v>
       </c>
       <c r="O17" t="n">
-        <v>178.3365374610834</v>
+        <v>560.9846007256435</v>
       </c>
       <c r="P17" t="n">
         <v>211.8739801603236</v>
@@ -36168,16 +36168,16 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K20" t="n">
-        <v>570.3215356263726</v>
+        <v>187.673472361809</v>
       </c>
       <c r="L20" t="n">
-        <v>232.8255376884422</v>
+        <v>615.4736009529988</v>
       </c>
       <c r="M20" t="n">
-        <v>655.0000000000006</v>
+        <v>655.000000000004</v>
       </c>
       <c r="N20" t="n">
-        <v>655.0000000000006</v>
+        <v>655.000000000004</v>
       </c>
       <c r="O20" t="n">
         <v>178.3365374610834</v>
@@ -36320,13 +36320,13 @@
         <v>96.11290668526664</v>
       </c>
       <c r="I22" t="n">
-        <v>162.2687738880801</v>
+        <v>162.2687738880785</v>
       </c>
       <c r="J22" t="n">
         <v>330.5205429673709</v>
       </c>
       <c r="K22" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -36411,19 +36411,19 @@
         <v>654.9999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>148.1470733148153</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>655.0000000000006</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>178.3365374610834</v>
+        <v>655.000000000004</v>
       </c>
       <c r="P23" t="n">
         <v>211.8739801603236</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>326.4836107758951</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36551,7 +36551,7 @@
         <v>44.61714403225807</v>
       </c>
       <c r="G25" t="n">
-        <v>74.61793043715912</v>
+        <v>74.61793043715849</v>
       </c>
       <c r="H25" t="n">
         <v>96.11290668526664</v>
@@ -36642,25 +36642,25 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K26" t="n">
-        <v>655</v>
+        <v>187.673472361809</v>
       </c>
       <c r="L26" t="n">
-        <v>654.9999999999999</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M26" t="n">
-        <v>655.0000000000001</v>
+        <v>655.0000000000074</v>
       </c>
       <c r="N26" t="n">
-        <v>148.1470733148155</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>178.3365374610834</v>
+        <v>655.0000000000074</v>
       </c>
       <c r="P26" t="n">
         <v>211.8739801603236</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>560.984600725633</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36800,7 +36800,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K28" t="n">
-        <v>107.3687343955783</v>
+        <v>107.3687343955782</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -36876,25 +36876,25 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>520.4824991852875</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K29" t="n">
-        <v>187.6734723618091</v>
+        <v>655</v>
       </c>
       <c r="L29" t="n">
-        <v>232.8255376884422</v>
+        <v>654.9999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>655.0000000000028</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>360.0210534751299</v>
       </c>
       <c r="O29" t="n">
-        <v>342.5538442998092</v>
+        <v>178.3365374610834</v>
       </c>
       <c r="P29" t="n">
-        <v>655.0000000000028</v>
+        <v>655.0000000000094</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -37122,13 +37122,13 @@
         <v>654.9999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>148.1470733148121</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>655.0000000000038</v>
+        <v>655.0000000000183</v>
       </c>
       <c r="O32" t="n">
-        <v>178.3365374610834</v>
+        <v>326.4836107758808</v>
       </c>
       <c r="P32" t="n">
         <v>211.8739801603236</v>
@@ -37137,7 +37137,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.033516706560146e-10</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -37274,7 +37274,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K34" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -37350,19 +37350,19 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>90.1777625991308</v>
+        <v>374.0000000000364</v>
       </c>
       <c r="K35" t="n">
+        <v>187.673472361809</v>
+      </c>
+      <c r="L35" t="n">
         <v>374</v>
       </c>
-      <c r="L35" t="n">
-        <v>373.9999999999999</v>
-      </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>252.500608668351</v>
+        <v>155.0048989056363</v>
       </c>
       <c r="O35" t="n">
         <v>178.3365374610834</v>
@@ -37432,19 +37432,19 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>22.69379302306083</v>
+        <v>318.5740338860743</v>
       </c>
       <c r="L36" t="n">
-        <v>192.8886405874496</v>
+        <v>374.0000000000364</v>
       </c>
       <c r="M36" t="n">
         <v>286.9650421645043</v>
       </c>
       <c r="N36" t="n">
-        <v>339.9353519954473</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>374</v>
+        <v>236.9437517198468</v>
       </c>
       <c r="P36" t="n">
         <v>264.4060611184268</v>
@@ -37499,7 +37499,7 @@
         <v>122.6171440322581</v>
       </c>
       <c r="G37" t="n">
-        <v>152.6179304371585</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>174.1129066852666</v>
@@ -37508,7 +37508,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>37.71390184794076</v>
+        <v>374.0000000000364</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -37535,13 +37535,13 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>46.15994652665276</v>
       </c>
       <c r="T37" t="n">
-        <v>189.8031384117751</v>
+        <v>56.49637668649029</v>
       </c>
       <c r="U37" t="n">
-        <v>246.0777070861978</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -37550,7 +37550,7 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>149.5563545698924</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -37587,10 +37587,10 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>374.0000000000455</v>
+        <v>374.0000000000637</v>
       </c>
       <c r="K38" t="n">
-        <v>187.6734723618091</v>
+        <v>187.673472361809</v>
       </c>
       <c r="L38" t="n">
         <v>232.8255376884422</v>
@@ -37599,7 +37599,7 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>296.179361217185</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>178.3365374610834</v>
@@ -37608,7 +37608,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>296.1793612171668</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37672,7 +37672,7 @@
         <v>318.5740338860743</v>
       </c>
       <c r="L39" t="n">
-        <v>243.7772067537692</v>
+        <v>57.40142568134173</v>
       </c>
       <c r="M39" t="n">
         <v>286.9650421645043</v>
@@ -37681,7 +37681,7 @@
         <v>339.9353519954473</v>
       </c>
       <c r="O39" t="n">
-        <v>46.59266649806909</v>
+        <v>232.9684475704963</v>
       </c>
       <c r="P39" t="n">
         <v>45.25534927787736</v>
@@ -37727,25 +37727,25 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>111.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>116.0190951630435</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>152.6179304371585</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>174.1129066852666</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>240.2687738880785</v>
       </c>
       <c r="J40" t="n">
-        <v>139.0578870620793</v>
+        <v>110.2264310164452</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -37772,7 +37772,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>46.15994652665276</v>
       </c>
       <c r="T40" t="n">
         <v>189.8031384117751</v>
@@ -37790,7 +37790,7 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>109.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -37824,16 +37824,16 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>374.0000000000692</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K41" t="n">
         <v>187.673472361809</v>
       </c>
       <c r="L41" t="n">
-        <v>232.8255376884422</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>206.0015986179906</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -37845,7 +37845,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q41" t="n">
-        <v>296.1793612171613</v>
+        <v>374.0000000001092</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37903,25 +37903,25 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>105.8536827519539</v>
+        <v>199.7892383131474</v>
       </c>
       <c r="K42" t="n">
-        <v>22.69379302306083</v>
+        <v>188.3512406398436</v>
       </c>
       <c r="L42" t="n">
         <v>374</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>286.9650421645043</v>
       </c>
       <c r="N42" t="n">
         <v>339.9353519954473</v>
       </c>
       <c r="O42" t="n">
-        <v>374</v>
+        <v>46.59266649806909</v>
       </c>
       <c r="P42" t="n">
-        <v>264.4060611184268</v>
+        <v>45.25534927787736</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -37979,13 +37979,13 @@
         <v>70.11290668526664</v>
       </c>
       <c r="I43" t="n">
-        <v>136.2687738880785</v>
+        <v>136.2687738880784</v>
       </c>
       <c r="J43" t="n">
         <v>304.5205429673709</v>
       </c>
       <c r="K43" t="n">
-        <v>81.36873439557826</v>
+        <v>81.36873439557824</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>85.80313841177508</v>
+        <v>85.80313841177507</v>
       </c>
       <c r="U43" t="n">
         <v>142.0777070861978</v>
@@ -38073,16 +38073,16 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>374.0000000001529</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>178.3365374610834</v>
+        <v>374.0000000002074</v>
       </c>
       <c r="P44" t="n">
-        <v>211.8739801603236</v>
+        <v>222.2121162390919</v>
       </c>
       <c r="Q44" t="n">
-        <v>206.0015986179469</v>
+        <v>374.0000000002074</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38140,22 +38140,22 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>199.7892383131474</v>
+        <v>158.8239925824821</v>
       </c>
       <c r="K45" t="n">
-        <v>318.5740338860743</v>
+        <v>22.69379302306083</v>
       </c>
       <c r="L45" t="n">
-        <v>57.40142568134173</v>
+        <v>374.0000000002074</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>286.9650421645043</v>
       </c>
       <c r="N45" t="n">
-        <v>339.9353519954473</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>300.7827778944511</v>
+        <v>374.0000000002074</v>
       </c>
       <c r="P45" t="n">
         <v>264.4060611184268</v>
